--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>31.8</v>
       </c>
       <c r="U2" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V2" t="n">
         <v>1000</v>
@@ -753,7 +753,7 @@
         <v>47.6</v>
       </c>
       <c r="U3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V3" t="n">
         <v>200</v>
@@ -846,10 +846,10 @@
         <v>122.7</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4" t="n">
-        <v>200</v>
+        <v>650</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         <v>141</v>
       </c>
       <c r="U5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V5" t="n">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
         <v>28.3</v>
       </c>
       <c r="U6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V6" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>141</v>
       </c>
       <c r="U8" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="V8" t="n">
         <v>30</v>
@@ -1311,7 +1311,7 @@
         <v>98.2</v>
       </c>
       <c r="U9" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V9" t="n">
         <v>350</v>
@@ -1404,7 +1404,7 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="V10" t="n">
         <v>600</v>
@@ -1497,7 +1497,7 @@
         <v>98.2</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V11" t="n">
         <v>350</v>
@@ -1590,7 +1590,7 @@
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="V12" t="n">
         <v>400</v>
@@ -1683,7 +1683,7 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="V13" t="n">
         <v>400</v>
@@ -1776,7 +1776,7 @@
         <v>141</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
         <v>200</v>
@@ -1962,10 +1962,10 @@
         <v>59.2</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>600</v>
+        <v>1400</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>31.8</v>
       </c>
       <c r="U18" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="V18" t="n">
         <v>300</v>
@@ -2239,7 +2239,7 @@
         <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="V19" t="n">
         <v>450</v>
@@ -2332,7 +2332,7 @@
         <v>184.9</v>
       </c>
       <c r="U20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V20" t="n">
         <v>200</v>
@@ -2425,7 +2425,7 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="V21" t="n">
         <v>450</v>
@@ -2518,10 +2518,10 @@
         <v>59.2</v>
       </c>
       <c r="U22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V22" t="n">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2611,10 +2611,10 @@
         <v>28.3</v>
       </c>
       <c r="U23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V23" t="n">
-        <v>350</v>
+        <v>900</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>139.7</v>
       </c>
       <c r="U24" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="V24" t="n">
         <v>600</v>
@@ -2797,10 +2797,10 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V25" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>139.7</v>
       </c>
       <c r="U26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V26" t="n">
         <v>300</v>
@@ -3074,9 +3074,11 @@
         <v>141</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>48000</v>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3256,7 +3258,7 @@
         <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
         <v>1100</v>
@@ -3349,7 +3351,7 @@
         <v>141</v>
       </c>
       <c r="U31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V31" t="n">
         <v>10</v>
@@ -3442,7 +3444,7 @@
         <v>122.7</v>
       </c>
       <c r="U32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V32" t="n">
         <v>650</v>
@@ -3535,7 +3537,7 @@
         <v>98.2</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V33" t="n">
         <v>10</v>
@@ -3628,7 +3630,7 @@
         <v>98.2</v>
       </c>
       <c r="U34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
         <v>10</v>
@@ -3721,7 +3723,7 @@
         <v>141</v>
       </c>
       <c r="U35" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V35" t="n">
         <v>200</v>
@@ -3817,7 +3819,7 @@
         <v>4</v>
       </c>
       <c r="V36" t="n">
-        <v>350</v>
+        <v>900</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -3907,7 +3909,7 @@
         <v>139.7</v>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V37" t="n">
         <v>1300</v>
@@ -4184,10 +4186,10 @@
         <v>59.2</v>
       </c>
       <c r="U40" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="V40" t="n">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4277,7 +4279,7 @@
         <v>59.2</v>
       </c>
       <c r="U41" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V41" t="n">
         <v>450</v>
@@ -4463,7 +4465,7 @@
         <v>47.6</v>
       </c>
       <c r="U43" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V43" t="n">
         <v>200</v>
@@ -4556,7 +4558,7 @@
         <v>139.7</v>
       </c>
       <c r="U44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V44" t="n">
         <v>1200</v>
@@ -4926,7 +4928,7 @@
         <v>31.8</v>
       </c>
       <c r="U48" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="V48" t="n">
         <v>30</v>
@@ -5019,7 +5021,7 @@
         <v>28.3</v>
       </c>
       <c r="U49" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V49" t="n">
         <v>600</v>
@@ -5205,7 +5207,7 @@
         <v>48.5</v>
       </c>
       <c r="U51" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="V51" t="n">
         <v>30</v>
@@ -5389,9 +5391,11 @@
         <v>59.2</v>
       </c>
       <c r="U53" t="n">
-        <v>1</v>
-      </c>
-      <c r="V53" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V53" t="n">
+        <v>4500</v>
+      </c>
       <c r="W53" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5480,10 +5484,10 @@
         <v>28.3</v>
       </c>
       <c r="U54" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V54" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -5666,10 +5670,10 @@
         <v>28.3</v>
       </c>
       <c r="U56" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="V56" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -6034,10 +6038,10 @@
         <v>141</v>
       </c>
       <c r="U60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V60" t="n">
-        <v>400</v>
+        <v>1800</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6311,7 +6315,7 @@
         <v>213.9</v>
       </c>
       <c r="U63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V63" t="n">
         <v>10</v>
@@ -6404,7 +6408,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6590,7 +6594,7 @@
         <v>270.6</v>
       </c>
       <c r="U66" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="V66" t="n">
         <v>700</v>
@@ -6867,9 +6871,11 @@
         <v>213.9</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1000</v>
+      </c>
       <c r="W69" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7233,7 +7239,7 @@
         <v>270.6</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V73" t="n">
         <v>1925</v>
@@ -7326,7 +7332,7 @@
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
@@ -7876,7 +7882,7 @@
         <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V80" t="n">
         <v>700</v>
@@ -8335,9 +8341,11 @@
         <v>213.9</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1000</v>
+      </c>
       <c r="W85" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10339,9 +10347,11 @@
         <v>129.6</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V107" t="n">
+        <v>300</v>
+      </c>
       <c r="W107" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13443,7 +13453,7 @@
         <v>37.9</v>
       </c>
       <c r="U141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V141" t="inlineStr"/>
       <c r="W141" t="inlineStr">

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -663,7 +663,7 @@
         <v>21</v>
       </c>
       <c r="V2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="V3" t="n">
         <v>1000</v>
@@ -831,7 +831,7 @@
         <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="n">
         <v>0.5</v>
@@ -846,7 +846,7 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V4" t="n">
         <v>1000</v>
@@ -1017,7 +1017,7 @@
         <v>10</v>
       </c>
       <c r="P6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q6" t="n">
         <v>0.5</v>
@@ -1035,7 +1035,7 @@
         <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>650</v>
+        <v>200</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>28.3</v>
       </c>
       <c r="U7" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V7" t="n">
         <v>500</v>
@@ -1203,7 +1203,7 @@
         <v>17</v>
       </c>
       <c r="P8" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q8" t="n">
         <v>0.5</v>
@@ -1218,7 +1218,7 @@
         <v>141</v>
       </c>
       <c r="U8" t="n">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="V8" t="n">
         <v>30</v>
@@ -1311,10 +1311,10 @@
         <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="V9" t="n">
-        <v>800</v>
+        <v>450</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V10" t="n">
         <v>600</v>
@@ -1497,10 +1497,10 @@
         <v>98.2</v>
       </c>
       <c r="U11" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="V11" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>19</v>
       </c>
       <c r="P13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q13" t="n">
         <v>0.5</v>
@@ -1752,7 +1752,7 @@
         <v>9976</v>
       </c>
       <c r="M14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N14" t="n">
         <v>31</v>
@@ -1869,7 +1869,7 @@
         <v>31.8</v>
       </c>
       <c r="U15" t="n">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="V15" t="n">
         <v>300</v>
@@ -1938,7 +1938,7 @@
         <v>17265</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
         <v>9</v>
@@ -2133,7 +2133,7 @@
         <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q18" t="n">
         <v>0.5</v>
@@ -2241,7 +2241,7 @@
         <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="V19" t="n">
         <v>450</v>
@@ -2334,7 +2334,7 @@
         <v>60.2</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
@@ -2503,7 +2503,7 @@
         <v>13</v>
       </c>
       <c r="P22" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q22" t="n">
         <v>0.5</v>
@@ -2518,7 +2518,7 @@
         <v>141</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V22" t="n">
         <v>200</v>
@@ -2704,7 +2704,7 @@
         <v>139.7</v>
       </c>
       <c r="U24" t="n">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="V24" t="n">
         <v>450</v>
@@ -2797,7 +2797,7 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V25" t="n">
         <v>600</v>
@@ -2983,10 +2983,10 @@
         <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>950</v>
+        <v>450</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>139.7</v>
       </c>
       <c r="U28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V28" t="n">
         <v>300</v>
@@ -3107,22 +3107,22 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>41.294052</v>
+        <v>41.272355</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>69.36799999999999</v>
+        <v>69.339643</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>41.294052, 69.368000</t>
+          <t>41.272355, 69.339643</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Тузель-3</t>
+          <t>Хосиятли махалля</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3142,19 +3142,19 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>8115</v>
+        <v>7321</v>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O29" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P29" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="Q29" t="n">
         <v>0.5</v>
@@ -3169,11 +3169,9 @@
         <v>141</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>48000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3186,7 +3184,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.294052,69.368000</t>
+          <t>https://www.google.com/maps?q=41.272355,69.339643</t>
         </is>
       </c>
     </row>
@@ -3203,19 +3201,19 @@
         <v>82</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>41.272355</v>
+        <v>41.315906</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>69.339643</v>
+        <v>69.297453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>41.272355, 69.339643</t>
+          <t>41.315906, 69.297453</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Хосиятли махалля</t>
+          <t>Ирригатор массив</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3231,23 +3229,23 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>7321</v>
+        <v>7188</v>
       </c>
       <c r="M30" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="O30" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="P30" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="Q30" t="n">
         <v>0.5</v>
@@ -3259,12 +3257,14 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>141</v>
+        <v>98.2</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="inlineStr"/>
+        <v>143</v>
+      </c>
+      <c r="V30" t="n">
+        <v>450</v>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272355,69.339643</t>
+          <t>https://www.google.com/maps?q=41.315906,69.297453</t>
         </is>
       </c>
     </row>
@@ -3294,19 +3294,19 @@
         <v>82</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>41.315906</v>
+        <v>41.25868</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>69.297453</v>
+        <v>69.339223</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>41.315906, 69.297453</t>
+          <t>41.258680, 69.339223</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ирригатор массив</t>
+          <t>Аханграбо (Панельный)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3315,30 +3315,30 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>7188</v>
+        <v>8057</v>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N31" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="O31" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="P31" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="Q31" t="n">
         <v>0.5</v>
@@ -3350,14 +3350,12 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>98.2</v>
+        <v>141</v>
       </c>
       <c r="U31" t="n">
-        <v>164</v>
-      </c>
-      <c r="V31" t="n">
-        <v>450</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3370,7 +3368,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.315906,69.297453</t>
+          <t>https://www.google.com/maps?q=41.258680,69.339223</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3420,7 @@
         <v>8138</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
         <v>21</v>
@@ -3480,19 +3478,19 @@
         <v>82</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>41.25868</v>
+        <v>41.294052</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>69.339223</v>
+        <v>69.36799999999999</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>41.258680, 69.339223</t>
+          <t>41.294052, 69.368000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Тузель-3</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3501,7 +3499,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3512,19 +3510,19 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>8057</v>
+        <v>8115</v>
       </c>
       <c r="M33" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
         <v>16</v>
       </c>
       <c r="O33" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="P33" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="Q33" t="n">
         <v>0.5</v>
@@ -3539,9 +3537,11 @@
         <v>141</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>48000</v>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.258680,69.339223</t>
+          <t>https://www.google.com/maps?q=41.294052,69.368000</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
         <v>12</v>
       </c>
       <c r="P34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q34" t="n">
         <v>0.5</v>
@@ -3630,7 +3630,7 @@
         <v>122.7</v>
       </c>
       <c r="U34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V34" t="n">
         <v>650</v>
@@ -3723,10 +3723,10 @@
         <v>141</v>
       </c>
       <c r="U35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V35" t="n">
-        <v>1100</v>
+        <v>10</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>41.252524</v>
@@ -3909,10 +3909,10 @@
         <v>98.2</v>
       </c>
       <c r="U37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V37" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -3943,24 +3943,24 @@
         <v>80</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>41.278439</v>
+        <v>41.359212</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>69.379378</v>
+        <v>69.172043</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>41.278439, 69.379378</t>
+          <t>41.359212, 69.172043</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Нурмухаммедов</t>
+          <t>Чигатай-Актепа</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -3971,23 +3971,23 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5429</v>
+        <v>2530</v>
       </c>
       <c r="M38" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N38" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="O38" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P38" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
         <v>0.5</v>
@@ -3999,12 +3999,14 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>141</v>
+        <v>184.9</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>250</v>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4017,7 +4019,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.278439,69.379378</t>
+          <t>https://www.google.com/maps?q=41.359212,69.172043</t>
         </is>
       </c>
     </row>
@@ -4034,24 +4036,24 @@
         <v>80</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>41.359212</v>
+        <v>41.278439</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>69.172043</v>
+        <v>69.379378</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>41.359212, 69.172043</t>
+          <t>41.278439, 69.379378</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Чигатай-Актепа</t>
+          <t>Нурмухаммедов</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -4062,23 +4064,23 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2530</v>
+        <v>5429</v>
       </c>
       <c r="M39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="O39" t="n">
+        <v>5</v>
+      </c>
+      <c r="P39" t="n">
         <v>11</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1</v>
       </c>
       <c r="Q39" t="n">
         <v>0.5</v>
@@ -4090,14 +4092,12 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>184.9</v>
+        <v>141</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" t="n">
-        <v>250</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.359212,69.172043</t>
+          <t>https://www.google.com/maps?q=41.278439,69.379378</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>41.386517</v>
@@ -4279,10 +4279,10 @@
         <v>139.7</v>
       </c>
       <c r="U41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V41" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4372,10 +4372,10 @@
         <v>59.2</v>
       </c>
       <c r="U42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V42" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4465,11 +4465,9 @@
         <v>139.7</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" t="n">
-        <v>6110</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4558,7 +4556,7 @@
         <v>47.6</v>
       </c>
       <c r="U44" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V44" t="n">
         <v>200</v>
@@ -4680,7 +4678,7 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>41.329268</v>
@@ -4926,7 +4924,7 @@
         <v>31.8</v>
       </c>
       <c r="U48" t="n">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="V48" t="n">
         <v>30</v>
@@ -5019,7 +5017,7 @@
         <v>28.3</v>
       </c>
       <c r="U49" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V49" t="n">
         <v>600</v>
@@ -5053,19 +5051,19 @@
         <v>74</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>41.310079</v>
+        <v>41.20054</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>69.24188599999999</v>
+        <v>69.246605</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>41.310079, 69.241886</t>
+          <t>41.200540, 69.246605</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Алмазар массив</t>
+          <t>Дарьябуйи махалля</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5074,30 +5072,30 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>12235</v>
+        <v>2723</v>
       </c>
       <c r="M50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="O50" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="P50" t="n">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="Q50" t="n">
         <v>0.5</v>
@@ -5109,13 +5107,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>28.3</v>
+        <v>122.7</v>
       </c>
       <c r="U50" t="n">
-        <v>119</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5129,7 +5127,7 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.310079,69.241886</t>
+          <t>https://www.google.com/maps?q=41.200540,69.246605</t>
         </is>
       </c>
     </row>
@@ -5146,19 +5144,19 @@
         <v>74</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>41.20054</v>
+        <v>41.310079</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>69.246605</v>
+        <v>69.24188599999999</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>41.200540, 69.246605</t>
+          <t>41.310079, 69.241886</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Дарьябуйи махалля</t>
+          <t>Алмазар массив</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5167,30 +5165,30 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2723</v>
+        <v>12235</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N51" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="O51" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="P51" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="Q51" t="n">
         <v>0.5</v>
@@ -5202,13 +5200,13 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>122.7</v>
+        <v>28.3</v>
       </c>
       <c r="U51" t="n">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="V51" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -5222,7 +5220,7 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.200540,69.246605</t>
+          <t>https://www.google.com/maps?q=41.310079,69.241886</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5281,7 @@
         <v>12</v>
       </c>
       <c r="P52" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q52" t="n">
         <v>0.5</v>
@@ -5298,7 +5296,7 @@
         <v>48.5</v>
       </c>
       <c r="U52" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="V52" t="n">
         <v>30</v>
@@ -5484,7 +5482,7 @@
         <v>60.2</v>
       </c>
       <c r="U54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
@@ -5759,7 +5757,7 @@
         <v>28.3</v>
       </c>
       <c r="U57" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="V57" t="n">
         <v>500</v>
@@ -5793,19 +5791,19 @@
         <v>72</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>41.258554</v>
+        <v>41.185516</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>69.15737900000001</v>
+        <v>69.226426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>41.258554, 69.157379</t>
+          <t>41.185516, 69.226426</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Аль-Хорезми-1</t>
+          <t>Чартак махалля</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5814,30 +5812,30 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>16260</v>
+        <v>2980</v>
       </c>
       <c r="M58" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="O58" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P58" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="Q58" t="n">
         <v>0.5</v>
@@ -5849,10 +5847,10 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>28.3</v>
+        <v>122.7</v>
       </c>
       <c r="U58" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="V58" t="n">
         <v>200</v>
@@ -5869,7 +5867,7 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.258554,69.157379</t>
+          <t>https://www.google.com/maps?q=41.185516,69.226426</t>
         </is>
       </c>
     </row>
@@ -5945,7 +5943,7 @@
         <v>31.8</v>
       </c>
       <c r="U59" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="V59" t="n">
         <v>300</v>
@@ -6038,7 +6036,7 @@
         <v>60.2</v>
       </c>
       <c r="U60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V60" t="n">
         <v>100</v>
@@ -6072,19 +6070,19 @@
         <v>71</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>41.185516</v>
+        <v>41.378753</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>69.226426</v>
+        <v>69.228041</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>41.185516, 69.226426</t>
+          <t>41.378753, 69.228041</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Чартак махалля</t>
+          <t>Ахил махалля</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6093,30 +6091,30 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2980</v>
+        <v>3771</v>
       </c>
       <c r="M61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
+        <v>14</v>
+      </c>
+      <c r="O61" t="n">
+        <v>6</v>
+      </c>
+      <c r="P61" t="n">
         <v>4</v>
-      </c>
-      <c r="O61" t="n">
-        <v>3</v>
-      </c>
-      <c r="P61" t="n">
-        <v>2</v>
       </c>
       <c r="Q61" t="n">
         <v>0.5</v>
@@ -6128,12 +6126,14 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>122.7</v>
+        <v>59.2</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V61" t="n">
+        <v>4500</v>
+      </c>
       <c r="W61" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.185516,69.226426</t>
+          <t>https://www.google.com/maps?q=41.378753,69.228041</t>
         </is>
       </c>
     </row>
@@ -6222,10 +6222,10 @@
         <v>213.9</v>
       </c>
       <c r="U62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V62" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>184.9</v>
       </c>
       <c r="U63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V63" t="n">
         <v>200</v>
@@ -6411,7 +6411,7 @@
         <v>3</v>
       </c>
       <c r="V64" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -6501,10 +6501,10 @@
         <v>270.6</v>
       </c>
       <c r="U65" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V65" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C67" t="n">
         <v>76</v>
@@ -6780,7 +6780,7 @@
         <v>213.9</v>
       </c>
       <c r="U68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V68" t="n">
         <v>300</v>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C73" t="n">
         <v>80</v>
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C75" t="n">
         <v>79</v>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C76" t="n">
         <v>81</v>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C77" t="n">
         <v>77</v>
@@ -7613,7 +7613,7 @@
         <v>270.6</v>
       </c>
       <c r="U77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
@@ -7639,10 +7639,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C78" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>41.276459</v>
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C79" t="n">
         <v>79</v>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C80" t="n">
         <v>84</v>
@@ -7886,10 +7886,10 @@
         <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V80" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C81" t="n">
         <v>79</v>
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C82" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>41.399172</v>
@@ -8282,7 +8282,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C85" t="n">
         <v>78</v>
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C86" t="n">
         <v>78</v>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C87" t="n">
         <v>82</v>
@@ -8529,7 +8529,7 @@
         <v>184.9</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr">
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C88" t="n">
         <v>80</v>
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C89" t="n">
         <v>77</v>
@@ -8739,7 +8739,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C90" t="n">
         <v>79</v>
@@ -8830,54 +8830,54 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C91" t="n">
         <v>76</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>41.445931</v>
+        <v>41.378499</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>69.475869</v>
+        <v>69.144857</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>41.445931, 69.475869</t>
+          <t>41.378499, 69.144857</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Сасбага</t>
+          <t>Илгар</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>3.1</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2143</v>
+        <v>2210</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>5</v>
       </c>
       <c r="R91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S91" t="n">
-        <v>129</v>
+        <v>2397</v>
       </c>
       <c r="T91" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -8905,12 +8905,12 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445931,69.475869</t>
+          <t>https://www.google.com/maps?q=41.378499,69.144857</t>
         </is>
       </c>
     </row>
@@ -8921,25 +8921,25 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C92" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>41.160793</v>
+        <v>41.445931</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>69.174412</v>
+        <v>69.475869</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>41.160793, 69.174412</t>
+          <t>41.445931, 69.475869</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Боборахим</t>
+          <t>Сасбага</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8948,18 +8948,18 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1726</v>
+        <v>2143</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -8977,13 +8977,13 @@
         <v>5</v>
       </c>
       <c r="R92" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S92" t="n">
-        <v>17092</v>
+        <v>129</v>
       </c>
       <c r="T92" t="n">
-        <v>129.6</v>
+        <v>213.9</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.160793,69.174412</t>
+          <t>https://www.google.com/maps?q=41.445931,69.475869</t>
         </is>
       </c>
     </row>
@@ -9012,25 +9012,25 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C93" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>41.421856</v>
+        <v>41.160793</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>69.209467</v>
+        <v>69.174412</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>41.421856, 69.209467</t>
+          <t>41.160793, 69.174412</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Куктерак</t>
+          <t>Боборахим</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9039,42 +9039,42 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J93" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2729</v>
+        <v>1726</v>
       </c>
       <c r="M93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
         <v>5</v>
       </c>
       <c r="R93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S93" t="n">
-        <v>187</v>
+        <v>17092</v>
       </c>
       <c r="T93" t="n">
-        <v>270.6</v>
+        <v>129.6</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -9087,12 +9087,12 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.421856,69.209467</t>
+          <t>https://www.google.com/maps?q=41.160793,69.174412</t>
         </is>
       </c>
     </row>
@@ -9103,25 +9103,25 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C94" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>41.363448</v>
+        <v>41.421856</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>69.124646</v>
+        <v>69.209467</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>41.363448, 69.124646</t>
+          <t>41.421856, 69.209467</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Шамсиабад</t>
+          <t>Куктерак</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9130,10 +9130,10 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -9141,28 +9141,28 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3339</v>
+        <v>2729</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N94" t="n">
         <v>4</v>
       </c>
       <c r="O94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q94" t="n">
         <v>5</v>
       </c>
       <c r="R94" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S94" t="n">
-        <v>2781</v>
+        <v>187</v>
       </c>
       <c r="T94" t="n">
         <v>270.6</v>
@@ -9183,7 +9183,7 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.363448,69.124646</t>
+          <t>https://www.google.com/maps?q=41.421856,69.209467</t>
         </is>
       </c>
     </row>
@@ -9194,25 +9194,25 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C95" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>41.413792</v>
+        <v>41.363448</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>69.181494</v>
+        <v>69.124646</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>41.413792, 69.181494</t>
+          <t>41.363448, 69.124646</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Масалбай</t>
+          <t>Шамсиабад</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9221,10 +9221,10 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J95" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -9232,28 +9232,28 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2319</v>
+        <v>3339</v>
       </c>
       <c r="M95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
         <v>4</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P95" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>5</v>
       </c>
       <c r="R95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S95" t="n">
-        <v>1267</v>
+        <v>2781</v>
       </c>
       <c r="T95" t="n">
         <v>270.6</v>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.413792,69.181494</t>
+          <t>https://www.google.com/maps?q=41.363448,69.124646</t>
         </is>
       </c>
     </row>
@@ -9285,25 +9285,25 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C96" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>41.404809</v>
+        <v>41.413792</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>69.391277</v>
+        <v>69.181494</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>41.404809, 69.391277</t>
+          <t>41.413792, 69.181494</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Уткир</t>
+          <t>Масалбай</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9312,30 +9312,30 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Кибрайский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1919</v>
+        <v>2319</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q96" t="n">
         <v>5</v>
@@ -9344,10 +9344,10 @@
         <v>2</v>
       </c>
       <c r="S96" t="n">
-        <v>1398</v>
+        <v>1267</v>
       </c>
       <c r="T96" t="n">
-        <v>213.9</v>
+        <v>270.6</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -9360,12 +9360,12 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
+          <t>https://www.google.com/maps?q=41.413792,69.181494</t>
         </is>
       </c>
     </row>
@@ -9376,25 +9376,25 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C97" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>41.173507</v>
+        <v>41.404809</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>69.131349</v>
+        <v>69.391277</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>41.173507, 69.131349</t>
+          <t>41.404809, 69.391277</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ханкурган</t>
+          <t>Уткир</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9403,18 +9403,18 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Кибрайский район</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2231</v>
+        <v>1919</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -9435,10 +9435,10 @@
         <v>2</v>
       </c>
       <c r="S97" t="n">
-        <v>2842</v>
+        <v>1398</v>
       </c>
       <c r="T97" t="n">
-        <v>184.9</v>
+        <v>213.9</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.173507,69.131349</t>
+          <t>https://www.google.com/maps?q=41.404809,69.391277</t>
         </is>
       </c>
     </row>
@@ -9467,45 +9467,45 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C98" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>41.445091</v>
+        <v>41.173507</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>69.249785</v>
+        <v>69.131349</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>41.445091, 69.249785</t>
+          <t>41.173507, 69.131349</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Чувалачи</t>
+          <t>Ханкурган</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
       <c r="J98" t="n">
         <v>5.3</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2773</v>
+        <v>2231</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -9523,13 +9523,13 @@
         <v>5</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>2842</v>
       </c>
       <c r="T98" t="n">
-        <v>270.6</v>
+        <v>184.9</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445091,69.249785</t>
+          <t>https://www.google.com/maps?q=41.173507,69.131349</t>
         </is>
       </c>
     </row>
@@ -9558,34 +9558,34 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C99" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>41.445517</v>
+        <v>41.445091</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>69.226005</v>
+        <v>69.249785</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>41.445517, 69.226005</t>
+          <t>41.445091, 69.249785</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Алишер Навои</t>
+          <t>Чувалачи</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J99" t="n">
         <v>5.3</v>
@@ -9596,7 +9596,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2065</v>
+        <v>2773</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -9614,10 +9614,10 @@
         <v>5</v>
       </c>
       <c r="R99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
         <v>270.6</v>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.445517,69.226005</t>
+          <t>https://www.google.com/maps?q=41.445091,69.249785</t>
         </is>
       </c>
     </row>
@@ -9649,25 +9649,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C100" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>41.273963</v>
+        <v>41.445517</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>69.055013</v>
+        <v>69.226005</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>41.273963, 69.055013</t>
+          <t>41.445517, 69.226005</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Тукимачи</t>
+          <t>Алишер Навои</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9676,18 +9676,18 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2760</v>
+        <v>2065</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -9705,13 +9705,13 @@
         <v>5</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="T100" t="n">
-        <v>184.9</v>
+        <v>270.6</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.273963,69.055013</t>
+          <t>https://www.google.com/maps?q=41.445517,69.226005</t>
         </is>
       </c>
     </row>
@@ -9740,69 +9740,69 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C101" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>41.432594</v>
+        <v>41.273963</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>69.542843</v>
+        <v>69.055013</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>41.432594, 69.542843</t>
+          <t>41.273963, 69.055013</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Вахид Хайдаров махалля</t>
+          <t>Тукимачи</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Город Чиpчик</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>5772</v>
+        <v>2760</v>
       </c>
       <c r="M101" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>5</v>
       </c>
       <c r="R101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>1599</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>40.8</v>
+        <v>184.9</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -9815,12 +9815,12 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.432594,69.542843</t>
+          <t>https://www.google.com/maps?q=41.273963,69.055013</t>
         </is>
       </c>
     </row>
@@ -9831,57 +9831,57 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C102" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>41.149854</v>
+        <v>41.432594</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>69.114925</v>
+        <v>69.542843</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>41.149854, 69.114925</t>
+          <t>41.432594, 69.542843</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Машраб</t>
+          <t>Вахид Хайдаров махалля</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J102" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Город Чиpчик</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2303</v>
+        <v>5772</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q102" t="n">
         <v>5</v>
@@ -9890,10 +9890,10 @@
         <v>2</v>
       </c>
       <c r="S102" t="n">
-        <v>829</v>
+        <v>1599</v>
       </c>
       <c r="T102" t="n">
-        <v>129.6</v>
+        <v>40.8</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9906,12 +9906,12 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.149854,69.114925</t>
+          <t>https://www.google.com/maps?q=41.432594,69.542843</t>
         </is>
       </c>
     </row>
@@ -9922,25 +9922,25 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C103" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>41.461777</v>
+        <v>41.149854</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>69.36531100000001</v>
+        <v>69.114925</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>41.461777, 69.365311</t>
+          <t>41.149854, 69.114925</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Гышткуприк</t>
+          <t>Машраб</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9949,18 +9949,18 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Ташкентский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2850</v>
+        <v>2303</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -9978,13 +9978,13 @@
         <v>5</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="T103" t="n">
-        <v>270.6</v>
+        <v>129.6</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.461777,69.365311</t>
+          <t>https://www.google.com/maps?q=41.149854,69.114925</t>
         </is>
       </c>
     </row>
@@ -10013,69 +10013,69 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C104" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>41.463379</v>
+        <v>41.461777</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>69.543897</v>
+        <v>69.36531100000001</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>41.463379, 69.543897</t>
+          <t>41.461777, 69.365311</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>8-й микрорайон</t>
+          <t>Гышткуприк</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J104" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Город Чиpчик</t>
+          <t>Ташкентский район</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>10093</v>
+        <v>2850</v>
       </c>
       <c r="M104" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>5</v>
       </c>
       <c r="R104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>1599</v>
+        <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>40.8</v>
+        <v>270.6</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -10088,12 +10088,12 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.463379,69.543897</t>
+          <t>https://www.google.com/maps?q=41.461777,69.365311</t>
         </is>
       </c>
     </row>
@@ -10104,25 +10104,25 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>41.457839</v>
+        <v>41.463379</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>69.56354399999999</v>
+        <v>69.543897</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>41.457839, 69.563544</t>
+          <t>41.463379, 69.543897</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>квартал Конструкторов</t>
+          <t>8-й микрорайон</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10131,10 +10131,10 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -10142,19 +10142,19 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>8420</v>
+        <v>10093</v>
       </c>
       <c r="M105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P105" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q105" t="n">
         <v>5</v>
@@ -10169,11 +10169,9 @@
         <v>40.8</v>
       </c>
       <c r="U105" t="n">
-        <v>1</v>
-      </c>
-      <c r="V105" t="n">
-        <v>2000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10186,7 +10184,7 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.457839,69.563544</t>
+          <t>https://www.google.com/maps?q=41.463379,69.543897</t>
         </is>
       </c>
     </row>
@@ -10197,74 +10195,76 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C106" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>41.061788</v>
+        <v>41.457839</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>69.352901</v>
+        <v>69.56354399999999</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>41.061788, 69.352901</t>
+          <t>41.457839, 69.563544</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Кумарык</t>
+          <t>квартал Конструкторов</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I106" t="n">
         <v>0.5</v>
       </c>
       <c r="J106" t="n">
-        <v>11.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Уртачирчикский район</t>
+          <t>Город Чиpчик</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2116</v>
+        <v>8420</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N106" t="n">
+        <v>4</v>
+      </c>
+      <c r="O106" t="n">
         <v>2</v>
       </c>
-      <c r="O106" t="n">
-        <v>1</v>
-      </c>
       <c r="P106" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Q106" t="n">
         <v>5</v>
       </c>
       <c r="R106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S106" t="n">
-        <v>1841</v>
+        <v>1599</v>
       </c>
       <c r="T106" t="n">
-        <v>134.2</v>
+        <v>40.8</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V106" t="n">
+        <v>2000</v>
+      </c>
       <c r="W106" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.061788,69.352901</t>
+          <t>https://www.google.com/maps?q=41.457839,69.563544</t>
         </is>
       </c>
     </row>
@@ -10288,76 +10288,74 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="C107" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>41.478034</v>
+        <v>41.061788</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>69.580118</v>
+        <v>69.352901</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>41.478034, 69.580118</t>
+          <t>41.061788, 69.352901</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Бахор махалля</t>
+          <t>Кумарык</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Город Чиpчик</t>
+          <t>Уртачирчикский район</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>18190</v>
+        <v>2116</v>
       </c>
       <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
         <v>2</v>
       </c>
-      <c r="N107" t="n">
-        <v>8</v>
-      </c>
       <c r="O107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P107" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q107" t="n">
         <v>5</v>
       </c>
       <c r="R107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S107" t="n">
-        <v>1995</v>
+        <v>1841</v>
       </c>
       <c r="T107" t="n">
-        <v>40.8</v>
+        <v>134.2</v>
       </c>
       <c r="U107" t="n">
-        <v>2</v>
-      </c>
-      <c r="V107" t="n">
-        <v>1000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10370,7 +10368,7 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.478034,69.580118</t>
+          <t>https://www.google.com/maps?q=41.061788,69.352901</t>
         </is>
       </c>
     </row>
@@ -10381,25 +10379,25 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C108" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>41.135337</v>
+        <v>41.478034</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>69.06326</v>
+        <v>69.580118</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>41.135337, 69.063260</t>
+          <t>41.478034, 69.580118</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Анаркулова массив</t>
+          <t>Бахор махалля</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10408,30 +10406,30 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J108" t="n">
-        <v>12.3</v>
+        <v>11.7</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Город Чиpчик</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>4982</v>
+        <v>18190</v>
       </c>
       <c r="M108" t="n">
         <v>2</v>
       </c>
       <c r="N108" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P108" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q108" t="n">
         <v>5</v>
@@ -10440,16 +10438,16 @@
         <v>3</v>
       </c>
       <c r="S108" t="n">
-        <v>909</v>
+        <v>1995</v>
       </c>
       <c r="T108" t="n">
-        <v>129.6</v>
+        <v>40.8</v>
       </c>
       <c r="U108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V108" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="W108" t="inlineStr">
         <is>
@@ -10463,7 +10461,7 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.135337,69.063260</t>
+          <t>https://www.google.com/maps?q=41.478034,69.580118</t>
         </is>
       </c>
     </row>
@@ -10474,37 +10472,37 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C109" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>41.107605</v>
+        <v>41.135337</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>69.08619299999999</v>
+        <v>69.06326</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>41.107605, 69.086193</t>
+          <t>41.135337, 69.063260</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ниязбаш</t>
+          <t>Анаркулова массив</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J109" t="n">
-        <v>12.9</v>
+        <v>12.3</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -10512,10 +10510,10 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2803</v>
+        <v>4982</v>
       </c>
       <c r="M109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N109" t="n">
         <v>6</v>
@@ -10524,7 +10522,7 @@
         <v>2</v>
       </c>
       <c r="P109" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q109" t="n">
         <v>5</v>
@@ -10539,9 +10537,11 @@
         <v>129.6</v>
       </c>
       <c r="U109" t="n">
-        <v>0</v>
-      </c>
-      <c r="V109" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V109" t="n">
+        <v>300</v>
+      </c>
       <c r="W109" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.107605,69.086193</t>
+          <t>https://www.google.com/maps?q=41.135337,69.063260</t>
         </is>
       </c>
     </row>
@@ -10565,25 +10565,25 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C110" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>41.463685</v>
+        <v>41.107605</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>69.611362</v>
+        <v>69.08619299999999</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>41.463685, 69.611362</t>
+          <t>41.107605, 69.086193</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Карабай</t>
+          <t>Ниязбаш</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10592,30 +10592,30 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2282</v>
+        <v>2803</v>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N110" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O110" t="n">
         <v>2</v>
       </c>
       <c r="P110" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q110" t="n">
         <v>5</v>
@@ -10624,10 +10624,10 @@
         <v>3</v>
       </c>
       <c r="S110" t="n">
-        <v>1995</v>
+        <v>909</v>
       </c>
       <c r="T110" t="n">
-        <v>147.5</v>
+        <v>129.6</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.463685,69.611362</t>
+          <t>https://www.google.com/maps?q=41.107605,69.086193</t>
         </is>
       </c>
     </row>
@@ -10656,25 +10656,25 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="C111" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>41.157616</v>
+        <v>41.463685</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>69.059894</v>
+        <v>69.611362</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>41.157616, 69.059894</t>
+          <t>41.463685, 69.611362</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Конкус</t>
+          <t>Карабай</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10683,30 +10683,30 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>13.1</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1815</v>
+        <v>2282</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q111" t="n">
         <v>5</v>
@@ -10715,10 +10715,10 @@
         <v>3</v>
       </c>
       <c r="S111" t="n">
-        <v>909</v>
+        <v>1995</v>
       </c>
       <c r="T111" t="n">
-        <v>129.6</v>
+        <v>147.5</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -10731,12 +10731,12 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.157616,69.059894</t>
+          <t>https://www.google.com/maps?q=41.463685,69.611362</t>
         </is>
       </c>
     </row>
@@ -10747,69 +10747,69 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C112" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>41.039806</v>
+        <v>41.157616</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>69.340406</v>
+        <v>69.059894</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>41.039806, 69.340406</t>
+          <t>41.157616, 69.059894</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Нурафшан (Тойтепа)</t>
+          <t>Конкус</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
-        <v>13.6</v>
+        <v>13.1</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Уртачирчикский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1871</v>
+        <v>1815</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
         <v>5</v>
       </c>
       <c r="R112" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S112" t="n">
-        <v>1946</v>
+        <v>909</v>
       </c>
       <c r="T112" t="n">
-        <v>134.2</v>
+        <v>129.6</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -10822,12 +10822,12 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.039806,69.340406</t>
+          <t>https://www.google.com/maps?q=41.157616,69.059894</t>
         </is>
       </c>
     </row>
@@ -10838,69 +10838,69 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C113" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>41.088745</v>
+        <v>41.039806</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>69.089637</v>
+        <v>69.340406</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>41.088745, 69.089637</t>
+          <t>41.039806, 69.340406</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ниязбаш</t>
+          <t>Нурафшан (Тойтепа)</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Уртачирчикский район</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2111</v>
+        <v>1871</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q113" t="n">
         <v>5</v>
       </c>
       <c r="R113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S113" t="n">
-        <v>909</v>
+        <v>1946</v>
       </c>
       <c r="T113" t="n">
-        <v>129.6</v>
+        <v>134.2</v>
       </c>
       <c r="U113" t="n">
         <v>0</v>
@@ -10913,12 +10913,12 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.088745,69.089637</t>
+          <t>https://www.google.com/maps?q=41.039806,69.340406</t>
         </is>
       </c>
     </row>
@@ -10929,69 +10929,69 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C114" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>41.034304</v>
+        <v>41.088745</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>69.359931</v>
+        <v>69.089637</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>41.034304, 69.359931</t>
+          <t>41.088745, 69.089637</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Нурафшан (Тойтепа)</t>
+          <t>Ниязбаш</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Уртачирчикский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2647</v>
+        <v>2111</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
         <v>5</v>
       </c>
       <c r="R114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S114" t="n">
-        <v>1946</v>
+        <v>909</v>
       </c>
       <c r="T114" t="n">
-        <v>134.2</v>
+        <v>129.6</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -11004,12 +11004,12 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.034304,69.359931</t>
+          <t>https://www.google.com/maps?q=41.088745,69.089637</t>
         </is>
       </c>
     </row>
@@ -11020,69 +11020,69 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C115" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>41.10839</v>
+        <v>41.034304</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>69.038905</v>
+        <v>69.359931</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>41.108390, 69.038905</t>
+          <t>41.034304, 69.359931</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Тонг массив</t>
+          <t>Нурафшан (Тойтепа)</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
-        <v>15.7</v>
+        <v>14.2</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Уртачирчикский район</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>4351</v>
+        <v>2647</v>
       </c>
       <c r="M115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P115" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q115" t="n">
         <v>5</v>
       </c>
       <c r="R115" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S115" t="n">
-        <v>909</v>
+        <v>1946</v>
       </c>
       <c r="T115" t="n">
-        <v>129.6</v>
+        <v>134.2</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -11100,7 +11100,7 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.108390,69.038905</t>
+          <t>https://www.google.com/maps?q=41.034304,69.359931</t>
         </is>
       </c>
     </row>
@@ -11111,69 +11111,69 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C116" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>41.02079</v>
+        <v>41.10839</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>69.351637</v>
+        <v>69.038905</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>41.020790, 69.351637</t>
+          <t>41.108390, 69.038905</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Чигирик</t>
+          <t>Тонг массив</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J116" t="n">
         <v>15.7</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Уртачирчикский район</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3239</v>
+        <v>4351</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N116" t="n">
+        <v>6</v>
+      </c>
+      <c r="O116" t="n">
         <v>2</v>
       </c>
-      <c r="O116" t="n">
-        <v>1</v>
-      </c>
       <c r="P116" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q116" t="n">
         <v>5</v>
       </c>
       <c r="R116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S116" t="n">
-        <v>1946</v>
+        <v>909</v>
       </c>
       <c r="T116" t="n">
-        <v>134.2</v>
+        <v>129.6</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.020790,69.351637</t>
+          <t>https://www.google.com/maps?q=41.108390,69.038905</t>
         </is>
       </c>
     </row>
@@ -11202,69 +11202,69 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="C117" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>41.135856</v>
+        <v>41.02079</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>69.03172000000001</v>
+        <v>69.351637</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>41.135856, 69.031720</t>
+          <t>41.020790, 69.351637</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Дангир</t>
+          <t>Чигирик</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
-        <v>16.3</v>
+        <v>15.7</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Янгиюльский район</t>
+          <t>Уртачирчикский район</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2313</v>
+        <v>3239</v>
       </c>
       <c r="M117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O117" t="n">
         <v>1</v>
       </c>
       <c r="P117" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q117" t="n">
         <v>5</v>
       </c>
       <c r="R117" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S117" t="n">
-        <v>909</v>
+        <v>1946</v>
       </c>
       <c r="T117" t="n">
-        <v>129.6</v>
+        <v>134.2</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.135856,69.031720</t>
+          <t>https://www.google.com/maps?q=41.020790,69.351637</t>
         </is>
       </c>
     </row>
@@ -11293,25 +11293,25 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="C118" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>41.514494</v>
+        <v>41.135856</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>69.636989</v>
+        <v>69.03172000000001</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>41.514494, 69.636989</t>
+          <t>41.135856, 69.031720</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Аранчи</t>
+          <t>Дангир</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11320,42 +11320,42 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J118" t="n">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Город Чиpчик</t>
+          <t>Янгиюльский район</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>4566</v>
+        <v>2313</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q118" t="n">
         <v>5</v>
       </c>
       <c r="R118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S118" t="n">
-        <v>444</v>
+        <v>909</v>
       </c>
       <c r="T118" t="n">
-        <v>40.8</v>
+        <v>129.6</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -11368,12 +11368,12 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.514494,69.636989</t>
+          <t>https://www.google.com/maps?q=41.135856,69.031720</t>
         </is>
       </c>
     </row>
@@ -11384,25 +11384,25 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C119" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>40.991527</v>
+        <v>41.514663</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>69.362544</v>
+        <v>69.629052</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>40.991527, 69.362544</t>
+          <t>41.514663, 69.629052</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Микрорайон</t>
+          <t>Бахт махалля</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -11411,27 +11411,27 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J119" t="n">
-        <v>18.9</v>
+        <v>17.5</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Уртачирчикский район</t>
+          <t>Город Чиpчик</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>6807</v>
+        <v>8262</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -11443,10 +11443,10 @@
         <v>2</v>
       </c>
       <c r="S119" t="n">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="T119" t="n">
-        <v>134.2</v>
+        <v>40.8</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -11459,12 +11459,12 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.991527,69.362544</t>
+          <t>https://www.google.com/maps?q=41.514663,69.629052</t>
         </is>
       </c>
     </row>
@@ -11475,45 +11475,45 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C120" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>41.531601</v>
+        <v>40.991527</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>69.637602</v>
+        <v>69.362544</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>41.531601, 69.637602</t>
+          <t>40.991527, 69.362544</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Азадбаш</t>
+          <t>Микрорайон</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J120" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Уртачирчикский район</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2381</v>
+        <v>6807</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -11534,10 +11534,10 @@
         <v>2</v>
       </c>
       <c r="S120" t="n">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="T120" t="n">
-        <v>147.5</v>
+        <v>134.2</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.531601,69.637602</t>
+          <t>https://www.google.com/maps?q=40.991527,69.362544</t>
         </is>
       </c>
     </row>
@@ -11566,7 +11566,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C121" t="n">
         <v>78</v>
@@ -12483,7 +12483,7 @@
         <v>7</v>
       </c>
       <c r="C131" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>41.572586</v>
@@ -12662,7 +12662,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C133" t="n">
         <v>51</v>
@@ -13455,7 +13455,7 @@
         <v>37.9</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V141" t="inlineStr"/>
       <c r="W141" t="inlineStr">
@@ -13484,7 +13484,7 @@
         <v>16</v>
       </c>
       <c r="C142" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>40.851248</v>
@@ -13666,7 +13666,7 @@
         <v>34</v>
       </c>
       <c r="C144" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>40.836641</v>
@@ -13848,7 +13848,7 @@
         <v>14</v>
       </c>
       <c r="C146" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>40.836137</v>
@@ -14209,10 +14209,10 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C150" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>40.808689</v>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C154" t="n">
         <v>58</v>
@@ -14846,10 +14846,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C157" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>40.957099</v>
@@ -15574,10 +15574,10 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C165" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>41.022527</v>
@@ -15756,7 +15756,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C167" t="n">
         <v>67</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C171" t="n">
         <v>51</v>
@@ -16396,7 +16396,7 @@
         <v>45</v>
       </c>
       <c r="C174" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D174" s="2" t="n">
         <v>40.976114</v>
@@ -16487,7 +16487,7 @@
         <v>17</v>
       </c>
       <c r="C175" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>40.990787</v>
@@ -16575,7 +16575,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C176" t="n">
         <v>67</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,10 +660,10 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V2" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="V3" t="n">
         <v>1000</v>
@@ -846,10 +846,10 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V4" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         <v>122.7</v>
       </c>
       <c r="U5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V5" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>139.7</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6" t="n">
         <v>1200</v>
@@ -1125,7 +1125,7 @@
         <v>28.3</v>
       </c>
       <c r="U7" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="V7" t="n">
         <v>500</v>
@@ -1218,7 +1218,7 @@
         <v>141</v>
       </c>
       <c r="U8" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V8" t="n">
         <v>918</v>
@@ -1311,7 +1311,7 @@
         <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="V9" t="n">
         <v>450</v>
@@ -1404,10 +1404,10 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="V10" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>59.2</v>
       </c>
       <c r="U11" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="V11" t="n">
         <v>450</v>
@@ -1590,7 +1590,7 @@
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V12" t="n">
         <v>350</v>
@@ -1683,10 +1683,10 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="V13" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>98.2</v>
       </c>
       <c r="U14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V14" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>98.2</v>
       </c>
       <c r="U15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V15" t="n">
         <v>350</v>
@@ -1965,7 +1965,7 @@
         <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>31.8</v>
       </c>
       <c r="U17" t="n">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="V17" t="n">
         <v>300</v>
@@ -2148,10 +2148,10 @@
         <v>48.5</v>
       </c>
       <c r="U18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>59.2</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
         <v>600</v>
@@ -2334,7 +2334,7 @@
         <v>98.2</v>
       </c>
       <c r="U20" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="V20" t="n">
         <v>350</v>
@@ -2429,7 +2429,9 @@
       <c r="U21" t="n">
         <v>3</v>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>3500</v>
+      </c>
       <c r="W21" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -2518,10 +2520,10 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="V22" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2611,10 +2613,10 @@
         <v>139.7</v>
       </c>
       <c r="U23" t="n">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="V23" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2704,7 +2706,7 @@
         <v>59.2</v>
       </c>
       <c r="U24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
         <v>600</v>
@@ -2800,7 +2802,7 @@
         <v>12</v>
       </c>
       <c r="V25" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2890,7 +2892,7 @@
         <v>139.7</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="V26" t="n">
         <v>300</v>
@@ -2983,7 +2985,7 @@
         <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="V27" t="n">
         <v>450</v>
@@ -3076,7 +3078,7 @@
         <v>139.7</v>
       </c>
       <c r="U28" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="V28" t="n">
         <v>450</v>
@@ -3169,7 +3171,7 @@
         <v>28.3</v>
       </c>
       <c r="U29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V29" t="n">
         <v>350</v>
@@ -3262,7 +3264,7 @@
         <v>139.7</v>
       </c>
       <c r="U30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V30" t="n">
         <v>300</v>
@@ -3355,7 +3357,7 @@
         <v>139.7</v>
       </c>
       <c r="U31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31" t="n">
         <v>700</v>
@@ -3448,7 +3450,7 @@
         <v>141</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V32" t="n">
         <v>1100</v>
@@ -3482,19 +3484,19 @@
         <v>81</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>41.25868</v>
+        <v>41.272355</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>69.339223</v>
+        <v>69.339643</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>41.258680, 69.339223</t>
+          <t>41.272355, 69.339643</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Хосиятли махалля</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3503,7 +3505,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3514,19 +3516,19 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>8057</v>
+        <v>7321</v>
       </c>
       <c r="M33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P33" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q33" t="n">
         <v>0.5</v>
@@ -3556,7 +3558,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.258680,69.339223</t>
+          <t>https://www.google.com/maps?q=41.272355,69.339643</t>
         </is>
       </c>
     </row>
@@ -3573,19 +3575,19 @@
         <v>81</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>41.272355</v>
+        <v>41.25868</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>69.339643</v>
+        <v>69.339223</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>41.272355, 69.339643</t>
+          <t>41.258680, 69.339223</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Хосиятли махалля</t>
+          <t>Аханграбо (Панельный)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3594,7 +3596,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3605,19 +3607,19 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>7321</v>
+        <v>8057</v>
       </c>
       <c r="M34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P34" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Q34" t="n">
         <v>0.5</v>
@@ -3632,11 +3634,9 @@
         <v>141</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
-      </c>
-      <c r="V34" t="n">
-        <v>300</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272355,69.339643</t>
+          <t>https://www.google.com/maps?q=41.258680,69.339223</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3725,7 @@
         <v>122.7</v>
       </c>
       <c r="U35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V35" t="n">
         <v>500</v>
@@ -3818,7 +3818,7 @@
         <v>141</v>
       </c>
       <c r="U36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V36" t="n">
         <v>10</v>
@@ -3911,7 +3911,7 @@
         <v>98.2</v>
       </c>
       <c r="U37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V37" t="n">
         <v>10</v>
@@ -4004,7 +4004,7 @@
         <v>98.2</v>
       </c>
       <c r="U38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V38" t="n">
         <v>350</v>
@@ -4097,10 +4097,10 @@
         <v>59.2</v>
       </c>
       <c r="U39" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="V39" t="n">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>98.2</v>
       </c>
       <c r="U40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V40" t="n">
         <v>10</v>
@@ -4283,7 +4283,7 @@
         <v>122.7</v>
       </c>
       <c r="U41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V41" t="n">
         <v>350</v>
@@ -4376,10 +4376,10 @@
         <v>47.6</v>
       </c>
       <c r="U42" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="V42" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>31.8</v>
       </c>
       <c r="U44" t="n">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="V44" t="n">
         <v>900</v>
@@ -4653,10 +4653,10 @@
         <v>28.3</v>
       </c>
       <c r="U45" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="V45" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>139.7</v>
       </c>
       <c r="U46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V46" t="n">
         <v>1000</v>
@@ -5023,7 +5023,7 @@
         <v>28.3</v>
       </c>
       <c r="U49" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="V49" t="n">
         <v>600</v>
@@ -5116,10 +5116,10 @@
         <v>28.3</v>
       </c>
       <c r="U50" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="V50" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5209,11 +5209,9 @@
         <v>139.7</v>
       </c>
       <c r="U51" t="n">
-        <v>2</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1575</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5304,7 +5302,9 @@
       <c r="U52" t="n">
         <v>3</v>
       </c>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="n">
+        <v>3500</v>
+      </c>
       <c r="W52" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5486,7 +5486,7 @@
         <v>31.8</v>
       </c>
       <c r="U54" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="V54" t="n">
         <v>300</v>
@@ -5765,7 +5765,7 @@
         <v>59.2</v>
       </c>
       <c r="U57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
@@ -5856,7 +5856,7 @@
         <v>59.2</v>
       </c>
       <c r="U58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V58" t="n">
         <v>6000</v>
@@ -6226,9 +6226,11 @@
         <v>213.9</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V62" t="n">
+        <v>700</v>
+      </c>
       <c r="W62" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6410,7 +6412,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6503,7 +6505,7 @@
         <v>184.9</v>
       </c>
       <c r="U65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V65" t="n">
         <v>200</v>
@@ -6596,7 +6598,7 @@
         <v>213.9</v>
       </c>
       <c r="U66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V66" t="n">
         <v>200</v>
@@ -6689,7 +6691,7 @@
         <v>270.6</v>
       </c>
       <c r="U67" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V67" t="n">
         <v>700</v>
@@ -6873,7 +6875,7 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V69" t="n">
         <v>300</v>
@@ -7059,7 +7061,7 @@
         <v>270.6</v>
       </c>
       <c r="U71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V71" t="n">
         <v>1925</v>
@@ -7702,9 +7704,11 @@
         <v>213.9</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V78" t="n">
+        <v>700</v>
+      </c>
       <c r="W78" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8068,9 +8072,11 @@
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1000</v>
+      </c>
       <c r="W82" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8159,7 +8165,7 @@
         <v>213.9</v>
       </c>
       <c r="U83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V83" t="n">
         <v>700</v>
@@ -10717,9 +10723,11 @@
         <v>40.8</v>
       </c>
       <c r="U111" t="n">
-        <v>1</v>
-      </c>
-      <c r="V111" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V111" t="n">
+        <v>1000</v>
+      </c>
       <c r="W111" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -11655,7 +11663,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C122" t="n">
         <v>52</v>
@@ -11746,7 +11754,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C123" t="n">
         <v>55</v>
@@ -12021,7 +12029,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C126" t="n">
         <v>57</v>
@@ -12112,7 +12120,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C127" t="n">
         <v>54</v>
@@ -12203,7 +12211,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C128" t="n">
         <v>63</v>
@@ -12294,7 +12302,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C129" t="n">
         <v>58</v>
@@ -12476,7 +12484,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C131" t="n">
         <v>61</v>
@@ -12567,7 +12575,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C132" t="n">
         <v>48</v>
@@ -12749,7 +12757,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C134" t="n">
         <v>58</v>
@@ -12840,7 +12848,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C135" t="n">
         <v>48</v>
@@ -12931,7 +12939,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C136" t="n">
         <v>56</v>
@@ -13022,7 +13030,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C137" t="n">
         <v>46</v>
@@ -13113,57 +13121,57 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C138" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>40.869157</v>
+        <v>40.853378</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>69.040657</v>
+        <v>69.601764</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>40.869157, 69.040657</t>
+          <t>40.853378, 69.601764</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Аккурган</t>
+          <t>Суюртепа</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>36.8</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Аккурганский район</t>
+          <t>Пскентский район</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>3068</v>
+        <v>14034</v>
       </c>
       <c r="M138" t="n">
+        <v>4</v>
+      </c>
+      <c r="N138" t="n">
+        <v>5</v>
+      </c>
+      <c r="O138" t="n">
         <v>2</v>
       </c>
-      <c r="N138" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" t="n">
-        <v>0</v>
-      </c>
       <c r="P138" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q138" t="n">
         <v>5</v>
@@ -13175,10 +13183,10 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>40.3</v>
+        <v>37.9</v>
       </c>
       <c r="U138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V138" t="inlineStr"/>
       <c r="W138" t="inlineStr">
@@ -13193,7 +13201,7 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.869157,69.040657</t>
+          <t>https://www.google.com/maps?q=40.853378,69.601764</t>
         </is>
       </c>
     </row>
@@ -13204,57 +13212,57 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C139" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>40.840055</v>
+        <v>40.869157</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>69.58559200000001</v>
+        <v>69.040657</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>40.840055, 69.585592</t>
+          <t>40.869157, 69.040657</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Узбекистан махалля</t>
+          <t>Аккурган</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
-        <v>37.8</v>
+        <v>36.8</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Пскентский район</t>
+          <t>Аккурганский район</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2262</v>
+        <v>3068</v>
       </c>
       <c r="M139" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N139" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q139" t="n">
         <v>5</v>
@@ -13266,7 +13274,7 @@
         <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>37.9</v>
+        <v>40.3</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -13284,7 +13292,7 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.840055,69.585592</t>
+          <t>https://www.google.com/maps?q=40.869157,69.040657</t>
         </is>
       </c>
     </row>
@@ -13295,57 +13303,57 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C140" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>40.825619</v>
+        <v>40.840055</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>69.188659</v>
+        <v>69.58559200000001</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>40.825619, 69.188659</t>
+          <t>40.840055, 69.585592</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Яхшибайтепа</t>
+          <t>Узбекистан махалля</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I140" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J140" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Пскентский район</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>2262</v>
+      </c>
+      <c r="M140" t="n">
+        <v>4</v>
+      </c>
+      <c r="N140" t="n">
+        <v>3</v>
+      </c>
+      <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="J140" t="n">
-        <v>38</v>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>Букинский район</t>
-        </is>
-      </c>
-      <c r="L140" t="n">
-        <v>1821</v>
-      </c>
-      <c r="M140" t="n">
-        <v>1</v>
-      </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
       <c r="P140" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q140" t="n">
         <v>5</v>
@@ -13357,10 +13365,10 @@
         <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>39.6</v>
+        <v>37.9</v>
       </c>
       <c r="U140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V140" t="inlineStr"/>
       <c r="W140" t="inlineStr">
@@ -13375,7 +13383,7 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.825619,69.188659</t>
+          <t>https://www.google.com/maps?q=40.840055,69.585592</t>
         </is>
       </c>
     </row>
@@ -13386,37 +13394,37 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C141" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>40.823418</v>
+        <v>40.825619</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>69.216067</v>
+        <v>69.188659</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>40.823418, 69.216067</t>
+          <t>40.825619, 69.188659</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Яхшибайтепа</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -13424,7 +13432,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2132</v>
+        <v>1821</v>
       </c>
       <c r="M141" t="n">
         <v>1</v>
@@ -13466,7 +13474,7 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.823418,69.216067</t>
+          <t>https://www.google.com/maps?q=40.825619,69.188659</t>
         </is>
       </c>
     </row>
@@ -13477,48 +13485,48 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C142" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>40.869928</v>
+        <v>40.823418</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>68.993559</v>
+        <v>69.216067</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>40.869928, 68.993559</t>
+          <t>40.823418, 69.216067</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Чакмак</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J142" t="n">
-        <v>38.5</v>
+        <v>38.1</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Букинский район</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1549</v>
+        <v>2132</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N142" t="n">
         <v>0</v>
@@ -13527,7 +13535,7 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q142" t="n">
         <v>5</v>
@@ -13539,7 +13547,7 @@
         <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>63.5</v>
+        <v>39.6</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -13552,12 +13560,12 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.869928,68.993559</t>
+          <t>https://www.google.com/maps?q=40.823418,69.216067</t>
         </is>
       </c>
     </row>
@@ -13568,57 +13576,57 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C143" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D143" s="2" t="n">
-        <v>40.836137</v>
+        <v>40.869928</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>69.609015</v>
+        <v>68.993559</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>40.836137, 69.609015</t>
+          <t>40.869928, 68.993559</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Юлдуз махалля</t>
+          <t>Чакмак</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J143" t="n">
-        <v>38.8</v>
+        <v>38.5</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Пскентский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>11060</v>
+        <v>1549</v>
       </c>
       <c r="M143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
         <v>5</v>
@@ -13630,7 +13638,7 @@
         <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>37.9</v>
+        <v>63.5</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -13643,12 +13651,12 @@
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.836137,69.609015</t>
+          <t>https://www.google.com/maps?q=40.869928,68.993559</t>
         </is>
       </c>
     </row>
@@ -13659,57 +13667,57 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="C144" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>40.805776</v>
+        <v>40.836137</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>69.246951</v>
+        <v>69.609015</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>40.805776, 69.246951</t>
+          <t>40.836137, 69.609015</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ачмайли</t>
+          <t>Юлдуз махалля</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I144" t="n">
         <v>0.4</v>
       </c>
       <c r="J144" t="n">
-        <v>39.9</v>
+        <v>38.8</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Букинский район</t>
+          <t>Пскентский район</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2059</v>
+        <v>11060</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q144" t="n">
         <v>5</v>
@@ -13721,7 +13729,7 @@
         <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>39.6</v>
+        <v>37.9</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -13734,12 +13742,12 @@
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.805776,69.246951</t>
+          <t>https://www.google.com/maps?q=40.836137,69.609015</t>
         </is>
       </c>
     </row>
@@ -13750,25 +13758,25 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C145" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>41.601553</v>
+        <v>40.805776</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>69.87878000000001</v>
+        <v>69.246951</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>41.601553, 69.878780</t>
+          <t>40.805776, 69.246951</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Каранккуль</t>
+          <t>Ачмайли</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -13777,18 +13785,18 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J145" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Букинский район</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1524</v>
+        <v>2059</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -13812,7 +13820,7 @@
         <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>147.5</v>
+        <v>39.6</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -13830,7 +13838,7 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.601553,69.878780</t>
+          <t>https://www.google.com/maps?q=40.805776,69.246951</t>
         </is>
       </c>
     </row>
@@ -13841,25 +13849,25 @@
         </is>
       </c>
       <c r="B146" t="n">
+        <v>36</v>
+      </c>
+      <c r="C146" t="n">
         <v>56</v>
       </c>
-      <c r="C146" t="n">
-        <v>48</v>
-      </c>
       <c r="D146" s="2" t="n">
-        <v>40.964208</v>
+        <v>41.601553</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>68.862195</v>
+        <v>69.87878000000001</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>40.964208, 68.862195</t>
+          <t>41.601553, 69.878780</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Алмазар</t>
+          <t>Каранккуль</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -13868,18 +13876,18 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J146" t="n">
         <v>40</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>3416</v>
+        <v>1524</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -13891,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
         <v>5</v>
@@ -13903,7 +13911,7 @@
         <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>59.7</v>
+        <v>147.5</v>
       </c>
       <c r="U146" t="n">
         <v>0</v>
@@ -13916,12 +13924,12 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.964208,68.862195</t>
+          <t>https://www.google.com/maps?q=41.601553,69.878780</t>
         </is>
       </c>
     </row>
@@ -13932,57 +13940,57 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C147" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>40.806913</v>
+        <v>40.964208</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>69.184213</v>
+        <v>68.862195</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>40.806913, 69.184213</t>
+          <t>40.964208, 68.862195</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмазар</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J147" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Букинский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>4987</v>
+        <v>3416</v>
       </c>
       <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
         <v>1</v>
-      </c>
-      <c r="N147" t="n">
-        <v>0</v>
-      </c>
-      <c r="O147" t="n">
-        <v>0</v>
-      </c>
-      <c r="P147" t="n">
-        <v>5</v>
       </c>
       <c r="Q147" t="n">
         <v>5</v>
@@ -13994,7 +14002,7 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>39.6</v>
+        <v>59.7</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -14012,7 +14020,7 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.806913,69.184213</t>
+          <t>https://www.google.com/maps?q=40.964208,68.862195</t>
         </is>
       </c>
     </row>
@@ -14023,34 +14031,34 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C148" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>40.804571</v>
+        <v>40.806913</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>69.219454</v>
+        <v>69.184213</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>40.804571, 69.219454</t>
+          <t>40.806913, 69.184213</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Чигатай</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J148" t="n">
         <v>40.2</v>
@@ -14061,7 +14069,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2767</v>
+        <v>4987</v>
       </c>
       <c r="M148" t="n">
         <v>1</v>
@@ -14073,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q148" t="n">
         <v>5</v>
@@ -14103,7 +14111,7 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.804571,69.219454</t>
+          <t>https://www.google.com/maps?q=40.806913,69.184213</t>
         </is>
       </c>
     </row>
@@ -14114,48 +14122,48 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C149" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>40.906695</v>
+        <v>40.804571</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>69.81593100000001</v>
+        <v>69.219454</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>40.906695, 69.815931</t>
+          <t>40.804571, 69.219454</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Нурабад</t>
+          <t>Чигатай</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J149" t="n">
-        <v>41.2</v>
+        <v>40.2</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Букинский район</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2251</v>
+        <v>2767</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N149" t="n">
         <v>0</v>
@@ -14164,7 +14172,7 @@
         <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q149" t="n">
         <v>5</v>
@@ -14176,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>55.2</v>
+        <v>39.6</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -14189,12 +14197,12 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.906695,69.815931</t>
+          <t>https://www.google.com/maps?q=40.804571,69.219454</t>
         </is>
       </c>
     </row>
@@ -14205,25 +14213,25 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C150" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>40.862328</v>
+        <v>40.906695</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>68.934483</v>
+        <v>69.81593100000001</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>40.862328, 68.934483</t>
+          <t>40.906695, 69.815931</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Дустабад (Солдатский)</t>
+          <t>Нурабад</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -14232,21 +14240,21 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
-        <v>41.7</v>
+        <v>41.2</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2450</v>
+        <v>2251</v>
       </c>
       <c r="M150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
         <v>0</v>
@@ -14255,7 +14263,7 @@
         <v>0</v>
       </c>
       <c r="P150" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
         <v>5</v>
@@ -14267,7 +14275,7 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>63.5</v>
+        <v>55.2</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -14280,12 +14288,12 @@
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.862328,68.934483</t>
+          <t>https://www.google.com/maps?q=40.906695,69.815931</t>
         </is>
       </c>
     </row>
@@ -14296,20 +14304,20 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C151" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>40.85233</v>
+        <v>40.862328</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>68.91854499999999</v>
+        <v>68.934483</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>40.852330, 68.918545</t>
+          <t>40.862328, 68.934483</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -14323,10 +14331,10 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J151" t="n">
-        <v>43.4</v>
+        <v>41.7</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -14334,7 +14342,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>3338</v>
+        <v>2450</v>
       </c>
       <c r="M151" t="n">
         <v>1</v>
@@ -14376,7 +14384,7 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.852330,68.918545</t>
+          <t>https://www.google.com/maps?q=40.862328,68.934483</t>
         </is>
       </c>
     </row>
@@ -14387,48 +14395,48 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C152" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>40.951358</v>
+        <v>40.85233</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>68.80686900000001</v>
+        <v>68.91854499999999</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>40.951358, 68.806869</t>
+          <t>40.852330, 68.918545</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Янги хаёт</t>
+          <t>Дустабад (Солдатский)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
-        <v>43.9</v>
+        <v>43.4</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2189</v>
+        <v>3338</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N152" t="n">
         <v>0</v>
@@ -14437,7 +14445,7 @@
         <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q152" t="n">
         <v>5</v>
@@ -14449,7 +14457,7 @@
         <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>59.7</v>
+        <v>63.5</v>
       </c>
       <c r="U152" t="n">
         <v>0</v>
@@ -14462,12 +14470,12 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.951358,68.806869</t>
+          <t>https://www.google.com/maps?q=40.852330,68.918545</t>
         </is>
       </c>
     </row>
@@ -14478,37 +14486,37 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C153" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>40.939688</v>
+        <v>40.951358</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>68.786965</v>
+        <v>68.80686900000001</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>40.939688, 68.786965</t>
+          <t>40.951358, 68.806869</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Чиназ</t>
+          <t>Янги хаёт</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="J153" t="n">
-        <v>45.9</v>
+        <v>43.9</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -14516,10 +14524,10 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1815</v>
+        <v>2189</v>
       </c>
       <c r="M153" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
         <v>0</v>
@@ -14528,7 +14536,7 @@
         <v>0</v>
       </c>
       <c r="P153" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
         <v>5</v>
@@ -14553,12 +14561,12 @@
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.939688,68.786965</t>
+          <t>https://www.google.com/maps?q=40.951358,68.806869</t>
         </is>
       </c>
     </row>
@@ -14569,69 +14577,69 @@
         </is>
       </c>
       <c r="B154" t="n">
+        <v>40</v>
+      </c>
+      <c r="C154" t="n">
+        <v>55</v>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>40.939688</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>68.786965</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>40.939688, 68.786965</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Чиназ</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>город</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
         <v>2</v>
       </c>
-      <c r="C154" t="n">
-        <v>79</v>
-      </c>
-      <c r="D154" s="2" t="n">
-        <v>41.639689</v>
-      </c>
-      <c r="E154" s="2" t="n">
-        <v>69.932056</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>41.639689, 69.932056</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Чарвак</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>город</t>
-        </is>
-      </c>
-      <c r="I154" t="n">
-        <v>0.8</v>
-      </c>
       <c r="J154" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2392</v>
+        <v>1815</v>
       </c>
       <c r="M154" t="n">
         <v>3</v>
       </c>
       <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
         <v>5</v>
-      </c>
-      <c r="O154" t="n">
-        <v>3</v>
-      </c>
-      <c r="P154" t="n">
-        <v>0</v>
       </c>
       <c r="Q154" t="n">
         <v>5</v>
       </c>
       <c r="R154" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S154" t="n">
-        <v>1260</v>
+        <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>147.5</v>
+        <v>59.7</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -14649,7 +14657,7 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.639689,69.932056</t>
+          <t>https://www.google.com/maps?q=40.939688,68.786965</t>
         </is>
       </c>
     </row>
@@ -14660,37 +14668,37 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C155" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>41.632465</v>
+        <v>41.639689</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>69.947683</v>
+        <v>69.932056</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>41.632465, 69.947683</t>
+          <t>41.639689, 69.932056</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Хoджикент</t>
+          <t>Чарвак</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J155" t="n">
-        <v>46.7</v>
+        <v>46</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -14698,7 +14706,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2646</v>
+        <v>2392</v>
       </c>
       <c r="M155" t="n">
         <v>3</v>
@@ -14740,7 +14748,7 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.632465,69.947683</t>
+          <t>https://www.google.com/maps?q=41.639689,69.932056</t>
         </is>
       </c>
     </row>
@@ -14751,25 +14759,25 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C156" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>40.955667</v>
+        <v>41.632465</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>68.74406399999999</v>
+        <v>69.947683</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>40.955667, 68.744064</t>
+          <t>41.632465, 69.947683</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Яллама</t>
+          <t>Хoджикент</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -14778,42 +14786,42 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J156" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Чиназский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2860</v>
+        <v>2646</v>
       </c>
       <c r="M156" t="n">
         <v>3</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P156" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
         <v>5</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="T156" t="n">
-        <v>59.7</v>
+        <v>147.5</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -14831,7 +14839,7 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.955667,68.744064</t>
+          <t>https://www.google.com/maps?q=41.632465,69.947683</t>
         </is>
       </c>
     </row>
@@ -14842,69 +14850,69 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C157" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>41.646154</v>
+        <v>40.955667</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>69.948246</v>
+        <v>68.74406399999999</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>41.646154, 69.948246</t>
+          <t>40.955667, 68.744064</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Бештут</t>
+          <t>Яллама</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J157" t="n">
-        <v>47.5</v>
+        <v>46.9</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Чиназский район</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1133</v>
+        <v>2860</v>
       </c>
       <c r="M157" t="n">
         <v>3</v>
       </c>
       <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
         <v>5</v>
-      </c>
-      <c r="O157" t="n">
-        <v>3</v>
-      </c>
-      <c r="P157" t="n">
-        <v>0</v>
       </c>
       <c r="Q157" t="n">
         <v>5</v>
       </c>
       <c r="R157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>1260</v>
+        <v>0</v>
       </c>
       <c r="T157" t="n">
-        <v>147.5</v>
+        <v>59.7</v>
       </c>
       <c r="U157" t="n">
         <v>0</v>
@@ -14922,7 +14930,7 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.646154,69.948246</t>
+          <t>https://www.google.com/maps?q=40.955667,68.744064</t>
         </is>
       </c>
     </row>
@@ -14933,54 +14941,54 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C158" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>40.90719</v>
+        <v>41.646154</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>68.790201</v>
+        <v>69.948246</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>40.907190, 68.790201</t>
+          <t>41.646154, 69.948246</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Курганча</t>
+          <t>Бештут</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J158" t="n">
-        <v>48.7</v>
+        <v>47.5</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Куйичирчикский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>2116</v>
+        <v>1133</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P158" t="n">
         <v>0</v>
@@ -14989,13 +14997,13 @@
         <v>5</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S158" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="T158" t="n">
-        <v>63.5</v>
+        <v>147.5</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>
@@ -15008,12 +15016,12 @@
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.907190,68.790201</t>
+          <t>https://www.google.com/maps?q=41.646154,69.948246</t>
         </is>
       </c>
     </row>
@@ -15024,25 +15032,25 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C159" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>40.773072</v>
+        <v>40.90719</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>68.963724</v>
+        <v>68.790201</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>40.773072, 68.963724</t>
+          <t>40.907190, 68.790201</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Хамзаабад</t>
+          <t>Курганча</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -15051,18 +15059,18 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J159" t="n">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Аккурганский район</t>
+          <t>Куйичирчикский район</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1867</v>
+        <v>2116</v>
       </c>
       <c r="M159" t="n">
         <v>0</v>
@@ -15086,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="T159" t="n">
-        <v>40.3</v>
+        <v>63.5</v>
       </c>
       <c r="U159" t="n">
         <v>0</v>
@@ -15104,7 +15112,7 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.773072,68.963724</t>
+          <t>https://www.google.com/maps?q=40.907190,68.790201</t>
         </is>
       </c>
     </row>
@@ -15115,25 +15123,25 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="C160" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>41.669921</v>
+        <v>40.773072</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>69.95719</v>
+        <v>68.963724</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>41.669921, 69.957190</t>
+          <t>40.773072, 68.963724</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Хумсан</t>
+          <t>Хамзаабад</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -15142,18 +15150,18 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J160" t="n">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Бостанлыкский район</t>
+          <t>Аккурганский район</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>2001</v>
+        <v>1867</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
@@ -15171,13 +15179,13 @@
         <v>5</v>
       </c>
       <c r="R160" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>1260</v>
+        <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>147.5</v>
+        <v>40.3</v>
       </c>
       <c r="U160" t="n">
         <v>0</v>
@@ -15195,7 +15203,7 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.669921,69.957190</t>
+          <t>https://www.google.com/maps?q=40.773072,68.963724</t>
         </is>
       </c>
     </row>
@@ -15206,25 +15214,25 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C161" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>41.022527</v>
+        <v>41.669921</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>70.044977</v>
+        <v>69.95719</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>41.022527, 70.044977</t>
+          <t>41.669921, 69.957190</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Самарчук</t>
+          <t>Хумсан</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -15233,24 +15241,24 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J161" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Бостанлыкский район</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1841</v>
+        <v>2001</v>
       </c>
       <c r="M161" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -15262,13 +15270,13 @@
         <v>5</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S161" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="T161" t="n">
-        <v>55.2</v>
+        <v>147.5</v>
       </c>
       <c r="U161" t="n">
         <v>0</v>
@@ -15281,12 +15289,12 @@
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.022527,70.044977</t>
+          <t>https://www.google.com/maps?q=41.669921,69.957190</t>
         </is>
       </c>
     </row>
@@ -15297,25 +15305,25 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C162" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>41.00906</v>
+        <v>41.022527</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>70.03652700000001</v>
+        <v>70.044977</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>41.009060, 70.036527</t>
+          <t>41.022527, 70.044977</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Саглам</t>
+          <t>Самарчук</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -15324,10 +15332,10 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J162" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -15335,10 +15343,10 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1664</v>
+        <v>1841</v>
       </c>
       <c r="M162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N162" t="n">
         <v>1</v>
@@ -15347,7 +15355,7 @@
         <v>0</v>
       </c>
       <c r="P162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
         <v>5</v>
@@ -15377,7 +15385,7 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.009060,70.036527</t>
+          <t>https://www.google.com/maps?q=41.022527,70.044977</t>
         </is>
       </c>
     </row>
@@ -15388,7 +15396,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C163" t="n">
         <v>55</v>
@@ -15479,7 +15487,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C164" t="n">
         <v>56</v>
@@ -15570,7 +15578,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C165" t="n">
         <v>66</v>
@@ -15661,7 +15669,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C166" t="n">
         <v>46</v>
@@ -15752,7 +15760,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C167" t="n">
         <v>57</v>
@@ -15843,7 +15851,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C168" t="n">
         <v>63</v>
@@ -15934,7 +15942,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C169" t="n">
         <v>48</v>
@@ -16116,7 +16124,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C171" t="n">
         <v>50</v>
@@ -16207,7 +16215,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C172" t="n">
         <v>65</v>
@@ -16389,7 +16397,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C174" t="n">
         <v>54</v>
@@ -16571,7 +16579,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C176" t="n">
         <v>61</v>
@@ -16662,7 +16670,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C177" t="n">
         <v>67</v>
@@ -16753,7 +16761,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C178" t="n">
         <v>51</v>
@@ -16844,7 +16852,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C179" t="n">
         <v>58</v>
@@ -16935,7 +16943,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C180" t="n">
         <v>66</v>
@@ -17026,7 +17034,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C181" t="n">
         <v>57</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,10 +660,10 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V2" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="V3" t="n">
         <v>1000</v>
@@ -831,7 +831,7 @@
         <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="n">
         <v>0.5</v>
@@ -846,10 +846,10 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V4" t="n">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>10</v>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q5" t="n">
         <v>0.5</v>
@@ -939,10 +939,10 @@
         <v>122.7</v>
       </c>
       <c r="U5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V5" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>139.7</v>
       </c>
       <c r="U6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V6" t="n">
         <v>1200</v>
@@ -1125,7 +1125,7 @@
         <v>28.3</v>
       </c>
       <c r="U7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V7" t="n">
         <v>500</v>
@@ -1203,7 +1203,7 @@
         <v>17</v>
       </c>
       <c r="P8" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q8" t="n">
         <v>0.5</v>
@@ -1218,7 +1218,7 @@
         <v>141</v>
       </c>
       <c r="U8" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="V8" t="n">
         <v>918</v>
@@ -1311,10 +1311,10 @@
         <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="V9" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V10" t="n">
         <v>1000</v>
@@ -1497,7 +1497,7 @@
         <v>59.2</v>
       </c>
       <c r="U11" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V11" t="n">
         <v>450</v>
@@ -1575,7 +1575,7 @@
         <v>19</v>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q12" t="n">
         <v>0.5</v>
@@ -1590,7 +1590,7 @@
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="V12" t="n">
         <v>350</v>
@@ -1683,10 +1683,10 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="V13" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>98.2</v>
       </c>
       <c r="U14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V14" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>98.2</v>
       </c>
       <c r="U15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V15" t="n">
         <v>350</v>
@@ -2055,7 +2055,7 @@
         <v>31.8</v>
       </c>
       <c r="U17" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="V17" t="n">
         <v>300</v>
@@ -2133,7 +2133,7 @@
         <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q18" t="n">
         <v>0.5</v>
@@ -2148,10 +2148,10 @@
         <v>48.5</v>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V18" t="n">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>59.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
         <v>600</v>
@@ -2319,7 +2319,7 @@
         <v>20</v>
       </c>
       <c r="P20" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q20" t="n">
         <v>0.5</v>
@@ -2334,7 +2334,7 @@
         <v>98.2</v>
       </c>
       <c r="U20" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="V20" t="n">
         <v>350</v>
@@ -2427,7 +2427,7 @@
         <v>60.2</v>
       </c>
       <c r="U21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
         <v>3500</v>
@@ -2520,7 +2520,7 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V22" t="n">
         <v>1000</v>
@@ -2613,7 +2613,7 @@
         <v>139.7</v>
       </c>
       <c r="U23" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="V23" t="n">
         <v>600</v>
@@ -2644,7 +2644,7 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>41.343199</v>
@@ -2706,7 +2706,7 @@
         <v>59.2</v>
       </c>
       <c r="U24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V24" t="n">
         <v>600</v>
@@ -2784,7 +2784,7 @@
         <v>13</v>
       </c>
       <c r="P25" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q25" t="n">
         <v>0.5</v>
@@ -2799,7 +2799,7 @@
         <v>141</v>
       </c>
       <c r="U25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V25" t="n">
         <v>200</v>
@@ -2985,10 +2985,10 @@
         <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V27" t="n">
-        <v>450</v>
+        <v>1260</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>139.7</v>
       </c>
       <c r="U28" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="V28" t="n">
         <v>450</v>
@@ -3171,7 +3171,7 @@
         <v>28.3</v>
       </c>
       <c r="U29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V29" t="n">
         <v>350</v>
@@ -3357,7 +3357,7 @@
         <v>139.7</v>
       </c>
       <c r="U31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V31" t="n">
         <v>700</v>
@@ -3450,10 +3450,10 @@
         <v>141</v>
       </c>
       <c r="U32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V32" t="n">
-        <v>1100</v>
+        <v>2600</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -3484,19 +3484,19 @@
         <v>81</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>41.272355</v>
+        <v>41.211644</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>69.339643</v>
+        <v>69.19953</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>41.272355, 69.339643</t>
+          <t>41.211644, 69.199530</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Хосиятли махалля</t>
+          <t>Сергели-9А</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3505,30 +3505,30 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>7321</v>
+        <v>19654</v>
       </c>
       <c r="M33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O33" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P33" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q33" t="n">
         <v>0.5</v>
@@ -3540,12 +3540,14 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>141</v>
+        <v>122.7</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="V33" t="n">
+        <v>500</v>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3558,7 +3560,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272355,69.339643</t>
+          <t>https://www.google.com/maps?q=41.211644,69.199530</t>
         </is>
       </c>
     </row>
@@ -3575,19 +3577,19 @@
         <v>81</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>41.25868</v>
+        <v>41.272355</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>69.339223</v>
+        <v>69.339643</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>41.258680, 69.339223</t>
+          <t>41.272355, 69.339643</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Хосиятли махалля</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3596,7 +3598,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3607,19 +3609,19 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>8057</v>
+        <v>7321</v>
       </c>
       <c r="M34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P34" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q34" t="n">
         <v>0.5</v>
@@ -3634,9 +3636,11 @@
         <v>141</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>300</v>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3649,7 +3653,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.258680,69.339223</t>
+          <t>https://www.google.com/maps?q=41.272355,69.339643</t>
         </is>
       </c>
     </row>
@@ -3666,19 +3670,19 @@
         <v>81</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>41.211644</v>
+        <v>41.25868</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>69.19953</v>
+        <v>69.339223</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>41.211644, 69.199530</t>
+          <t>41.258680, 69.339223</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Сергели-9А</t>
+          <t>Аханграбо (Панельный)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3687,30 +3691,30 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>19654</v>
+        <v>8057</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O35" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q35" t="n">
         <v>0.5</v>
@@ -3722,14 +3726,12 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>122.7</v>
+        <v>141</v>
       </c>
       <c r="U35" t="n">
-        <v>7</v>
-      </c>
-      <c r="V35" t="n">
-        <v>500</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3742,7 +3744,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.211644,69.199530</t>
+          <t>https://www.google.com/maps?q=41.258680,69.339223</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3913,7 @@
         <v>98.2</v>
       </c>
       <c r="U37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V37" t="n">
         <v>10</v>
@@ -4004,7 +4006,7 @@
         <v>98.2</v>
       </c>
       <c r="U38" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V38" t="n">
         <v>350</v>
@@ -4038,24 +4040,24 @@
         <v>78</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>41.330879</v>
+        <v>41.334298</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>69.22666</v>
+        <v>69.226758</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>41.330879, 69.226660</t>
+          <t>41.334298, 69.226758</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Старый Город</t>
+          <t>Чигатай Дарваза махалля</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>район города</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -4070,19 +4072,19 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>11177</v>
+        <v>10288</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N39" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="O39" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P39" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Q39" t="n">
         <v>0.5</v>
@@ -4097,10 +4099,10 @@
         <v>59.2</v>
       </c>
       <c r="U39" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="V39" t="n">
-        <v>250</v>
+        <v>650</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4114,7 +4116,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.330879,69.226660</t>
+          <t>https://www.google.com/maps?q=41.334298,69.226758</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4192,7 @@
         <v>98.2</v>
       </c>
       <c r="U40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V40" t="n">
         <v>10</v>
@@ -4283,7 +4285,7 @@
         <v>122.7</v>
       </c>
       <c r="U41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V41" t="n">
         <v>350</v>
@@ -4376,10 +4378,10 @@
         <v>47.6</v>
       </c>
       <c r="U42" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V42" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4560,7 +4562,7 @@
         <v>31.8</v>
       </c>
       <c r="U44" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="V44" t="n">
         <v>900</v>
@@ -4653,10 +4655,10 @@
         <v>28.3</v>
       </c>
       <c r="U45" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V45" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -4746,7 +4748,7 @@
         <v>139.7</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
         <v>1000</v>
@@ -4839,7 +4841,7 @@
         <v>60.2</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
@@ -5116,7 +5118,7 @@
         <v>28.3</v>
       </c>
       <c r="U50" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="V50" t="n">
         <v>600</v>
@@ -5209,9 +5211,11 @@
         <v>139.7</v>
       </c>
       <c r="U51" t="n">
-        <v>1</v>
-      </c>
-      <c r="V51" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1575</v>
+      </c>
       <c r="W51" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5300,7 +5304,7 @@
         <v>60.2</v>
       </c>
       <c r="U52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V52" t="n">
         <v>3500</v>
@@ -5486,7 +5490,7 @@
         <v>31.8</v>
       </c>
       <c r="U54" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V54" t="n">
         <v>300</v>
@@ -5675,7 +5679,7 @@
         <v>4</v>
       </c>
       <c r="V56" t="n">
-        <v>100</v>
+        <v>3500</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -5765,9 +5769,11 @@
         <v>59.2</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V57" t="n">
+        <v>16000</v>
+      </c>
       <c r="W57" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5856,7 +5862,7 @@
         <v>59.2</v>
       </c>
       <c r="U58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V58" t="n">
         <v>6000</v>
@@ -6319,7 +6325,7 @@
         <v>184.9</v>
       </c>
       <c r="U63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V63" t="n">
         <v>6000</v>
@@ -6412,7 +6418,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6505,7 +6511,7 @@
         <v>184.9</v>
       </c>
       <c r="U65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V65" t="n">
         <v>200</v>
@@ -6598,7 +6604,7 @@
         <v>213.9</v>
       </c>
       <c r="U66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V66" t="n">
         <v>200</v>
@@ -6691,7 +6697,7 @@
         <v>270.6</v>
       </c>
       <c r="U67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V67" t="n">
         <v>700</v>
@@ -7245,7 +7251,7 @@
         <v>184.9</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
@@ -7522,7 +7528,7 @@
         <v>270.6</v>
       </c>
       <c r="U76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr">
@@ -8624,7 +8630,7 @@
         <v>184.9</v>
       </c>
       <c r="U88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr">
@@ -8834,7 +8840,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C91" t="n">
         <v>77</v>
@@ -10108,7 +10114,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C105" t="n">
         <v>77</v>
@@ -10355,9 +10361,11 @@
         <v>40.8</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V107" t="n">
+        <v>2000</v>
+      </c>
       <c r="W107" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10630,7 +10638,7 @@
         <v>40.8</v>
       </c>
       <c r="U110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V110" t="n">
         <v>700</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,10 +660,10 @@
         <v>31.8</v>
       </c>
       <c r="U2" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="V2" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>47.6</v>
       </c>
       <c r="U3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V3" t="n">
         <v>300</v>
@@ -846,7 +846,7 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V4" t="n">
         <v>1000</v>
@@ -939,7 +939,7 @@
         <v>139.7</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
         <v>1260</v>
@@ -1032,7 +1032,7 @@
         <v>122.7</v>
       </c>
       <c r="U6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="V6" t="n">
         <v>130</v>
@@ -1125,7 +1125,7 @@
         <v>28.3</v>
       </c>
       <c r="U7" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="V7" t="n">
         <v>500</v>
@@ -1218,10 +1218,10 @@
         <v>141</v>
       </c>
       <c r="U8" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="V8" t="n">
-        <v>918</v>
+        <v>954</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V9" t="n">
         <v>450</v>
@@ -1407,7 +1407,7 @@
         <v>13</v>
       </c>
       <c r="V10" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>98.2</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V11" t="n">
         <v>350</v>
@@ -1590,7 +1590,7 @@
         <v>98.2</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V12" t="n">
         <v>1000</v>
@@ -1683,10 +1683,10 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V13" t="n">
-        <v>350</v>
+        <v>1300</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>141</v>
       </c>
       <c r="U14" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="V14" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>31.8</v>
       </c>
       <c r="U15" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="V15" t="n">
         <v>300</v>
@@ -1962,7 +1962,7 @@
         <v>141</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
         <v>200</v>
@@ -2148,7 +2148,7 @@
         <v>48.5</v>
       </c>
       <c r="U18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18" t="n">
         <v>1000</v>
@@ -2334,7 +2334,7 @@
         <v>122.7</v>
       </c>
       <c r="U20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V20" t="n">
         <v>350</v>
@@ -2520,7 +2520,7 @@
         <v>141</v>
       </c>
       <c r="U22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V22" t="n">
         <v>200</v>
@@ -2613,10 +2613,10 @@
         <v>59.2</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V23" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>139.7</v>
       </c>
       <c r="U24" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="V24" t="n">
         <v>600</v>
@@ -2802,7 +2802,7 @@
         <v>19</v>
       </c>
       <c r="V25" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>139.7</v>
       </c>
       <c r="U26" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V26" t="n">
         <v>300</v>
@@ -2985,7 +2985,7 @@
         <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V27" t="n">
         <v>450</v>
@@ -3078,7 +3078,7 @@
         <v>28.3</v>
       </c>
       <c r="U28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V28" t="n">
         <v>350</v>
@@ -3171,7 +3171,7 @@
         <v>270.6</v>
       </c>
       <c r="U29" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V29" t="n">
         <v>300</v>
@@ -3264,10 +3264,10 @@
         <v>139.7</v>
       </c>
       <c r="U30" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V30" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3357,10 +3357,10 @@
         <v>98.2</v>
       </c>
       <c r="U31" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="V31" t="n">
-        <v>800</v>
+        <v>954</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>139.7</v>
       </c>
       <c r="U32" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V32" t="n">
         <v>300</v>
@@ -3636,7 +3636,7 @@
         <v>141</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V34" t="n">
         <v>2600</v>
@@ -3823,7 +3823,7 @@
         <v>9</v>
       </c>
       <c r="V36" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>141</v>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V37" t="n">
         <v>10</v>
@@ -4006,7 +4006,7 @@
         <v>98.2</v>
       </c>
       <c r="U38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V38" t="n">
         <v>10</v>
@@ -4192,7 +4192,7 @@
         <v>98.2</v>
       </c>
       <c r="U40" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V40" t="n">
         <v>350</v>
@@ -4378,7 +4378,7 @@
         <v>59.2</v>
       </c>
       <c r="U42" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="V42" t="n">
         <v>250</v>
@@ -4471,7 +4471,7 @@
         <v>59.2</v>
       </c>
       <c r="U43" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="V43" t="n">
         <v>10</v>
@@ -4564,7 +4564,7 @@
         <v>98.2</v>
       </c>
       <c r="U44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V44" t="n">
         <v>10</v>
@@ -4844,7 +4844,7 @@
         <v>2</v>
       </c>
       <c r="V47" t="n">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -4934,10 +4934,10 @@
         <v>122.7</v>
       </c>
       <c r="U48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V48" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -4968,19 +4968,19 @@
         <v>75</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>41.240101</v>
+        <v>41.299391</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>69.326797</v>
+        <v>69.26531</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>41.240101, 69.326797</t>
+          <t>41.299391, 69.265310</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Куйлюк Центр</t>
+          <t>Багсарай махалля</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4989,30 +4989,30 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>6255</v>
+        <v>11879</v>
       </c>
       <c r="M49" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N49" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="P49" t="n">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="Q49" t="n">
         <v>0.5</v>
@@ -5024,12 +5024,14 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>60.2</v>
+        <v>31.8</v>
       </c>
       <c r="U49" t="n">
-        <v>2</v>
-      </c>
-      <c r="V49" t="inlineStr"/>
+        <v>107</v>
+      </c>
+      <c r="V49" t="n">
+        <v>900</v>
+      </c>
       <c r="W49" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5042,7 +5044,7 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.240101,69.326797</t>
+          <t>https://www.google.com/maps?q=41.299391,69.265310</t>
         </is>
       </c>
     </row>
@@ -5059,19 +5061,19 @@
         <v>75</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>41.299391</v>
+        <v>41.240101</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>69.26531</v>
+        <v>69.326797</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>41.299391, 69.265310</t>
+          <t>41.240101, 69.326797</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Багсарай махалля</t>
+          <t>Куйлюк Центр</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5080,30 +5082,30 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>11879</v>
+        <v>6255</v>
       </c>
       <c r="M50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N50" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="O50" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="Q50" t="n">
         <v>0.5</v>
@@ -5115,14 +5117,12 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>31.8</v>
+        <v>60.2</v>
       </c>
       <c r="U50" t="n">
-        <v>97</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1200</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.299391,69.265310</t>
+          <t>https://www.google.com/maps?q=41.240101,69.326797</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
         <v>28.3</v>
       </c>
       <c r="U51" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="V51" t="n">
         <v>250</v>
@@ -5304,7 +5304,7 @@
         <v>28.3</v>
       </c>
       <c r="U52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V52" t="n">
         <v>550</v>
@@ -5397,11 +5397,9 @@
         <v>139.7</v>
       </c>
       <c r="U53" t="n">
-        <v>3</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1575</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5431,19 +5429,19 @@
         <v>73</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>41.283644</v>
+        <v>41.271397</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>69.28462</v>
+        <v>69.20517700000001</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>41.283644, 69.284620</t>
+          <t>41.271397, 69.205177</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Сарыкулька</t>
+          <t>Наккашлык</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5452,30 +5450,30 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>5986</v>
+        <v>10663</v>
       </c>
       <c r="M54" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N54" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="O54" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P54" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="Q54" t="n">
         <v>0.5</v>
@@ -5487,13 +5485,13 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>48.5</v>
+        <v>28.3</v>
       </c>
       <c r="U54" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="V54" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -5507,7 +5505,7 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.283644,69.284620</t>
+          <t>https://www.google.com/maps?q=41.271397,69.205177</t>
         </is>
       </c>
     </row>
@@ -5524,19 +5522,19 @@
         <v>73</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>41.254507</v>
+        <v>41.283644</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>69.37862699999999</v>
+        <v>69.28462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>41.254507, 69.378627</t>
+          <t>41.283644, 69.284620</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Сувсоз-2 (Водник)</t>
+          <t>Сарыкулька</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5545,30 +5543,30 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>10644</v>
+        <v>5986</v>
       </c>
       <c r="M55" t="n">
         <v>5</v>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="O55" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="Q55" t="n">
         <v>0.5</v>
@@ -5580,13 +5578,13 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>60.2</v>
+        <v>48.5</v>
       </c>
       <c r="U55" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="V55" t="n">
-        <v>1800</v>
+        <v>1000</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -5600,7 +5598,7 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.254507,69.378627</t>
+          <t>https://www.google.com/maps?q=41.283644,69.284620</t>
         </is>
       </c>
     </row>
@@ -5617,19 +5615,19 @@
         <v>73</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>41.271397</v>
+        <v>41.254507</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>69.20517700000001</v>
+        <v>69.37862699999999</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>41.271397, 69.205177</t>
+          <t>41.254507, 69.378627</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Наккашлык</t>
+          <t>Сувсоз-2 (Водник)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5638,30 +5636,30 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>10663</v>
+        <v>10644</v>
       </c>
       <c r="M56" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="O56" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="P56" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
         <v>0.5</v>
@@ -5673,13 +5671,13 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>28.3</v>
+        <v>60.2</v>
       </c>
       <c r="U56" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="V56" t="n">
-        <v>600</v>
+        <v>1800</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -5693,7 +5691,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271397,69.205177</t>
+          <t>https://www.google.com/maps?q=41.254507,69.378627</t>
         </is>
       </c>
     </row>
@@ -5769,10 +5767,10 @@
         <v>139.7</v>
       </c>
       <c r="U57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V57" t="n">
-        <v>1300</v>
+        <v>1700</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -5803,51 +5801,51 @@
         <v>73</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>41.238019</v>
+        <v>41.366713</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>69.346493</v>
+        <v>69.23165299999999</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>41.238019, 69.346493</t>
+          <t>41.366713, 69.231653</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Бузаучи</t>
+          <t>Каракамыш 1/4</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>4072</v>
+        <v>5172</v>
       </c>
       <c r="M58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N58" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P58" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Q58" t="n">
         <v>0.5</v>
@@ -5859,13 +5857,13 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>60.2</v>
+        <v>59.2</v>
       </c>
       <c r="U58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V58" t="n">
-        <v>3500</v>
+        <v>10</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -5879,7 +5877,7 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.238019,69.346493</t>
+          <t>https://www.google.com/maps?q=41.366713,69.231653</t>
         </is>
       </c>
     </row>
@@ -5896,51 +5894,51 @@
         <v>73</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>41.366713</v>
+        <v>41.238019</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>69.23165299999999</v>
+        <v>69.346493</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>41.366713, 69.231653</t>
+          <t>41.238019, 69.346493</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Каракамыш 1/4</t>
+          <t>Бузаучи</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>5172</v>
+        <v>4072</v>
       </c>
       <c r="M59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N59" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="O59" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P59" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q59" t="n">
         <v>0.5</v>
@@ -5952,13 +5950,13 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>59.2</v>
+        <v>60.2</v>
       </c>
       <c r="U59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V59" t="n">
-        <v>10</v>
+        <v>3500</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -5972,7 +5970,7 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.366713,69.231653</t>
+          <t>https://www.google.com/maps?q=41.238019,69.346493</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6046,7 @@
         <v>28.3</v>
       </c>
       <c r="U60" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="V60" t="n">
         <v>600</v>
@@ -6141,7 +6139,7 @@
         <v>31.8</v>
       </c>
       <c r="U61" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="V61" t="n">
         <v>300</v>
@@ -6234,7 +6232,7 @@
         <v>184.9</v>
       </c>
       <c r="U62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V62" t="n">
         <v>200</v>
@@ -6327,7 +6325,7 @@
         <v>184.9</v>
       </c>
       <c r="U63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V63" t="n">
         <v>200</v>
@@ -6699,7 +6697,7 @@
         <v>213.9</v>
       </c>
       <c r="U67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V67" t="n">
         <v>200</v>
@@ -6792,10 +6790,10 @@
         <v>270.6</v>
       </c>
       <c r="U68" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V68" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -6885,7 +6883,7 @@
         <v>213.9</v>
       </c>
       <c r="U69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V69" t="n">
         <v>700</v>
@@ -6913,7 +6911,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C70" t="n">
         <v>75</v>
@@ -7069,7 +7067,7 @@
         <v>270.6</v>
       </c>
       <c r="U71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V71" t="n">
         <v>300</v>
@@ -7281,7 +7279,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C74" t="n">
         <v>86</v>
@@ -7530,7 +7528,7 @@
         <v>270.6</v>
       </c>
       <c r="U76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V76" t="n">
         <v>1925</v>
@@ -8080,10 +8078,10 @@
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V82" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -8264,7 +8262,7 @@
         <v>184.9</v>
       </c>
       <c r="U84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V84" t="n">
         <v>200</v>
@@ -8388,7 +8386,7 @@
         <v>40</v>
       </c>
       <c r="C86" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>41.417442</v>
@@ -8476,7 +8474,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C87" t="n">
         <v>78</v>
@@ -8661,7 +8659,7 @@
         <v>51</v>
       </c>
       <c r="C89" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>41.44656</v>
@@ -9022,7 +9020,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C93" t="n">
         <v>81</v>
@@ -9295,7 +9293,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C96" t="n">
         <v>81</v>
@@ -9750,7 +9748,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C101" t="n">
         <v>78</v>
@@ -9936,7 +9934,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C103" t="n">
         <v>75</v>
@@ -10118,7 +10116,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C105" t="n">
         <v>82</v>
@@ -10300,7 +10298,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C107" t="n">
         <v>86</v>
@@ -10458,11 +10456,9 @@
         <v>129.6</v>
       </c>
       <c r="U108" t="n">
-        <v>1</v>
-      </c>
-      <c r="V108" t="n">
-        <v>300</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10854,7 +10850,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C113" t="n">
         <v>82</v>
@@ -12590,7 +12586,7 @@
         <v>6</v>
       </c>
       <c r="C132" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>41.612566</v>
@@ -12954,7 +12950,7 @@
         <v>52</v>
       </c>
       <c r="C136" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>40.84809</v>
@@ -13045,7 +13041,7 @@
         <v>56</v>
       </c>
       <c r="C137" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>40.968917</v>
@@ -13562,7 +13558,7 @@
         <v>37.9</v>
       </c>
       <c r="U142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V142" t="inlineStr"/>
       <c r="W142" t="inlineStr">
@@ -14043,7 +14039,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C148" t="n">
         <v>57</v>
@@ -14592,7 +14588,7 @@
         <v>9</v>
       </c>
       <c r="C154" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>41.624384</v>
@@ -14680,10 +14676,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C155" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>40.939688</v>
@@ -16500,7 +16496,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C175" t="n">
         <v>62</v>
@@ -16864,7 +16860,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C179" t="n">
         <v>62</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="V2" t="n">
         <v>200</v>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="V3" t="n">
         <v>500</v>
@@ -846,7 +846,7 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="V4" t="n">
         <v>1000</v>
@@ -1032,7 +1032,7 @@
         <v>28.3</v>
       </c>
       <c r="U6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V6" t="n">
         <v>500</v>
@@ -1125,10 +1125,10 @@
         <v>139.7</v>
       </c>
       <c r="U7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V7" t="n">
-        <v>300</v>
+        <v>730</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>141</v>
       </c>
       <c r="U8" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="V8" t="n">
         <v>300</v>
@@ -1311,7 +1311,7 @@
         <v>98.2</v>
       </c>
       <c r="U9" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="V9" t="n">
         <v>1200</v>
@@ -1497,7 +1497,7 @@
         <v>139.7</v>
       </c>
       <c r="U11" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="V11" t="n">
         <v>600</v>
@@ -1593,7 +1593,7 @@
         <v>6</v>
       </c>
       <c r="V12" t="n">
-        <v>1000</v>
+        <v>1700</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V13" t="n">
-        <v>1300</v>
+        <v>350</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
         <v>141</v>
       </c>
       <c r="U15" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="V15" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>48.5</v>
       </c>
       <c r="U16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V16" t="n">
         <v>1000</v>
@@ -2055,7 +2055,7 @@
         <v>31.8</v>
       </c>
       <c r="U17" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="V17" t="n">
         <v>300</v>
@@ -2241,7 +2241,7 @@
         <v>60.2</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
         <v>3500</v>
@@ -2334,7 +2334,7 @@
         <v>59.2</v>
       </c>
       <c r="U20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V20" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="V21" t="n">
         <v>600</v>
@@ -2520,7 +2520,7 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V22" t="n">
         <v>600</v>
@@ -2613,7 +2613,7 @@
         <v>59.2</v>
       </c>
       <c r="U23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V23" t="n">
         <v>600</v>
@@ -2706,10 +2706,10 @@
         <v>141</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V24" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V25" t="n">
         <v>450</v>
@@ -2985,10 +2985,10 @@
         <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V27" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3078,9 +3078,11 @@
         <v>141</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>300</v>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3353,10 +3355,10 @@
         <v>122.7</v>
       </c>
       <c r="U31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V31" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3632,10 +3634,10 @@
         <v>98.2</v>
       </c>
       <c r="U34" t="n">
+        <v>9</v>
+      </c>
+      <c r="V34" t="n">
         <v>10</v>
-      </c>
-      <c r="V34" t="n">
-        <v>200</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3725,10 +3727,10 @@
         <v>141</v>
       </c>
       <c r="U35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V35" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3818,10 +3820,10 @@
         <v>98.2</v>
       </c>
       <c r="U36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V36" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -3911,7 +3913,7 @@
         <v>59.2</v>
       </c>
       <c r="U37" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="V37" t="n">
         <v>250</v>
@@ -4004,7 +4006,7 @@
         <v>59.2</v>
       </c>
       <c r="U38" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V38" t="n">
         <v>10</v>
@@ -4097,9 +4099,11 @@
         <v>139.7</v>
       </c>
       <c r="U39" t="n">
-        <v>3</v>
-      </c>
-      <c r="V39" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1575</v>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4463,7 +4467,7 @@
         <v>31.8</v>
       </c>
       <c r="U43" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="V43" t="n">
         <v>300</v>
@@ -4556,7 +4560,7 @@
         <v>28.3</v>
       </c>
       <c r="U44" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="V44" t="n">
         <v>250</v>
@@ -4649,7 +4653,7 @@
         <v>60.2</v>
       </c>
       <c r="U45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V45" t="n">
         <v>3500</v>
@@ -4742,11 +4746,9 @@
         <v>60.2</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1800</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4835,7 +4837,7 @@
         <v>139.7</v>
       </c>
       <c r="U47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V47" t="n">
         <v>1200</v>
@@ -4928,7 +4930,7 @@
         <v>28.3</v>
       </c>
       <c r="U48" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="V48" t="n">
         <v>600</v>
@@ -5021,7 +5023,7 @@
         <v>60.2</v>
       </c>
       <c r="U49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V49" t="n">
         <v>100</v>
@@ -5114,10 +5116,10 @@
         <v>28.3</v>
       </c>
       <c r="U50" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="V50" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5207,7 +5209,7 @@
         <v>59.2</v>
       </c>
       <c r="U51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V51" t="n">
         <v>10</v>
@@ -5300,7 +5302,7 @@
         <v>31.8</v>
       </c>
       <c r="U52" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="V52" t="n">
         <v>300</v>
@@ -5393,7 +5395,7 @@
         <v>59.2</v>
       </c>
       <c r="U53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V53" t="n">
         <v>6000</v>
@@ -5577,7 +5579,7 @@
         <v>28.3</v>
       </c>
       <c r="U55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V55" t="n">
         <v>600</v>
@@ -5854,7 +5856,7 @@
         <v>122.7</v>
       </c>
       <c r="U58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V58" t="n">
         <v>130</v>
@@ -5947,7 +5949,7 @@
         <v>122.7</v>
       </c>
       <c r="U59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V59" t="n">
         <v>130</v>
@@ -6040,7 +6042,7 @@
         <v>28.3</v>
       </c>
       <c r="U60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V60" t="n">
         <v>350</v>
@@ -6133,9 +6135,11 @@
         <v>122.7</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V61" t="n">
+        <v>21000</v>
+      </c>
       <c r="W61" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6227,7 +6231,7 @@
         <v>4</v>
       </c>
       <c r="V62" t="n">
-        <v>300</v>
+        <v>730</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -6410,7 +6414,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6503,7 +6507,7 @@
         <v>184.9</v>
       </c>
       <c r="U65" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V65" t="n">
         <v>200</v>
@@ -6689,7 +6693,7 @@
         <v>184.9</v>
       </c>
       <c r="U67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V67" t="n">
         <v>250</v>
@@ -6782,7 +6786,7 @@
         <v>270.6</v>
       </c>
       <c r="U68" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V68" t="n">
         <v>700</v>
@@ -6875,10 +6879,10 @@
         <v>213.9</v>
       </c>
       <c r="U69" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V69" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -7062,7 +7066,7 @@
         <v>3</v>
       </c>
       <c r="V71" t="n">
-        <v>1925</v>
+        <v>6000</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
@@ -7702,11 +7706,9 @@
         <v>270.6</v>
       </c>
       <c r="U78" t="n">
-        <v>1</v>
-      </c>
-      <c r="V78" t="n">
-        <v>1925</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8436,11 +8438,9 @@
         <v>270.6</v>
       </c>
       <c r="U86" t="n">
-        <v>1</v>
-      </c>
-      <c r="V86" t="n">
-        <v>1925</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9985,11 +9985,9 @@
         <v>184.9</v>
       </c>
       <c r="U103" t="n">
-        <v>1</v>
-      </c>
-      <c r="V103" t="n">
-        <v>600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10537,7 +10535,7 @@
         <v>40.8</v>
       </c>
       <c r="U109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V109" t="n">
         <v>700</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="V2" t="n">
         <v>200</v>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="V3" t="n">
         <v>500</v>
@@ -846,7 +846,7 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V4" t="n">
         <v>1000</v>
@@ -939,10 +939,10 @@
         <v>122.7</v>
       </c>
       <c r="U5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>28.3</v>
       </c>
       <c r="U6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V6" t="n">
         <v>500</v>
@@ -1128,7 +1128,7 @@
         <v>14</v>
       </c>
       <c r="V7" t="n">
-        <v>730</v>
+        <v>300</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>141</v>
       </c>
       <c r="U8" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="V8" t="n">
         <v>300</v>
@@ -1311,7 +1311,7 @@
         <v>98.2</v>
       </c>
       <c r="U9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="V9" t="n">
         <v>1200</v>
@@ -1404,10 +1404,10 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="V10" t="n">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>139.7</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="V11" t="n">
         <v>600</v>
@@ -1590,10 +1590,10 @@
         <v>98.2</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12" t="n">
-        <v>1700</v>
+        <v>1000</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V13" t="n">
         <v>350</v>
@@ -1779,7 +1779,7 @@
         <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>141</v>
       </c>
       <c r="U15" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V15" t="n">
         <v>350</v>
@@ -1962,7 +1962,7 @@
         <v>48.5</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
         <v>1000</v>
@@ -2055,7 +2055,7 @@
         <v>31.8</v>
       </c>
       <c r="U17" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="V17" t="n">
         <v>300</v>
@@ -2148,7 +2148,7 @@
         <v>59.2</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
         <v>600</v>
@@ -2427,7 +2427,7 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="V21" t="n">
         <v>600</v>
@@ -2520,7 +2520,7 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V22" t="n">
         <v>600</v>
@@ -2709,7 +2709,7 @@
         <v>5</v>
       </c>
       <c r="V24" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -2799,10 +2799,10 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="V25" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>98.2</v>
       </c>
       <c r="U26" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="V26" t="n">
         <v>800</v>
@@ -2985,10 +2985,10 @@
         <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V27" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3355,10 +3355,10 @@
         <v>122.7</v>
       </c>
       <c r="U31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V31" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>98.2</v>
       </c>
       <c r="U34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V34" t="n">
         <v>10</v>
@@ -3730,7 +3730,7 @@
         <v>10</v>
       </c>
       <c r="V35" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3820,10 +3820,10 @@
         <v>98.2</v>
       </c>
       <c r="U36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
-        <v>700</v>
+        <v>4199</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -3913,10 +3913,10 @@
         <v>59.2</v>
       </c>
       <c r="U37" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="V37" t="n">
-        <v>250</v>
+        <v>650</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>59.2</v>
       </c>
       <c r="U38" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V38" t="n">
         <v>10</v>
@@ -4099,11 +4099,9 @@
         <v>139.7</v>
       </c>
       <c r="U39" t="n">
-        <v>4</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1575</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4192,7 +4190,7 @@
         <v>47.6</v>
       </c>
       <c r="U40" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V40" t="n">
         <v>200</v>
@@ -4467,7 +4465,7 @@
         <v>31.8</v>
       </c>
       <c r="U43" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="V43" t="n">
         <v>300</v>
@@ -4560,10 +4558,10 @@
         <v>28.3</v>
       </c>
       <c r="U44" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="V44" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4653,10 +4651,10 @@
         <v>60.2</v>
       </c>
       <c r="U45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V45" t="n">
-        <v>3500</v>
+        <v>1200</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -4746,9 +4744,11 @@
         <v>60.2</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1800</v>
+      </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4837,7 +4837,7 @@
         <v>139.7</v>
       </c>
       <c r="U47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V47" t="n">
         <v>1200</v>
@@ -4930,7 +4930,7 @@
         <v>28.3</v>
       </c>
       <c r="U48" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="V48" t="n">
         <v>600</v>
@@ -5023,7 +5023,7 @@
         <v>60.2</v>
       </c>
       <c r="U49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V49" t="n">
         <v>100</v>
@@ -5116,7 +5116,7 @@
         <v>28.3</v>
       </c>
       <c r="U50" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V50" t="n">
         <v>500</v>
@@ -5209,7 +5209,7 @@
         <v>59.2</v>
       </c>
       <c r="U51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V51" t="n">
         <v>10</v>
@@ -5302,7 +5302,7 @@
         <v>31.8</v>
       </c>
       <c r="U52" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="V52" t="n">
         <v>300</v>
@@ -5395,7 +5395,7 @@
         <v>59.2</v>
       </c>
       <c r="U53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V53" t="n">
         <v>6000</v>
@@ -5579,7 +5579,7 @@
         <v>28.3</v>
       </c>
       <c r="U55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="V55" t="n">
         <v>600</v>
@@ -5765,7 +5765,7 @@
         <v>59.2</v>
       </c>
       <c r="U57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
@@ -5856,10 +5856,10 @@
         <v>122.7</v>
       </c>
       <c r="U58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V58" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -5949,10 +5949,10 @@
         <v>122.7</v>
       </c>
       <c r="U59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V59" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>28.3</v>
       </c>
       <c r="U60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V60" t="n">
         <v>350</v>
@@ -6231,7 +6231,7 @@
         <v>4</v>
       </c>
       <c r="V62" t="n">
-        <v>730</v>
+        <v>300</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -6321,10 +6321,10 @@
         <v>213.9</v>
       </c>
       <c r="U63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V63" t="n">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V64" t="n">
         <v>200</v>
@@ -6507,7 +6507,7 @@
         <v>184.9</v>
       </c>
       <c r="U65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V65" t="n">
         <v>200</v>
@@ -6600,7 +6600,7 @@
         <v>184.9</v>
       </c>
       <c r="U66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V66" t="n">
         <v>500</v>
@@ -6786,7 +6786,7 @@
         <v>270.6</v>
       </c>
       <c r="U68" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="V68" t="n">
         <v>700</v>
@@ -6879,7 +6879,7 @@
         <v>213.9</v>
       </c>
       <c r="U69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V69" t="n">
         <v>350</v>
@@ -7063,7 +7063,7 @@
         <v>270.6</v>
       </c>
       <c r="U71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V71" t="n">
         <v>6000</v>
@@ -7431,7 +7431,7 @@
         <v>270.6</v>
       </c>
       <c r="U75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
@@ -7613,10 +7613,10 @@
         <v>213.9</v>
       </c>
       <c r="U77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V77" t="n">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="W77" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V82" t="n">
         <v>700</v>
@@ -9985,9 +9985,11 @@
         <v>184.9</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
-      </c>
-      <c r="V103" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V103" t="n">
+        <v>600</v>
+      </c>
       <c r="W103" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10442,11 +10444,9 @@
         <v>129.6</v>
       </c>
       <c r="U108" t="n">
-        <v>1</v>
-      </c>
-      <c r="V108" t="n">
-        <v>300</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr">
         <is>
           <t>рекомендуемая</t>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V2" t="n">
         <v>200</v>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="V3" t="n">
         <v>500</v>
@@ -846,7 +846,7 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V4" t="n">
         <v>1000</v>
@@ -939,10 +939,10 @@
         <v>122.7</v>
       </c>
       <c r="U5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V5" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>28.3</v>
       </c>
       <c r="U6" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="V6" t="n">
         <v>500</v>
@@ -1125,7 +1125,7 @@
         <v>139.7</v>
       </c>
       <c r="U7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V7" t="n">
         <v>300</v>
@@ -1218,7 +1218,7 @@
         <v>141</v>
       </c>
       <c r="U8" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="V8" t="n">
         <v>300</v>
@@ -1311,7 +1311,7 @@
         <v>98.2</v>
       </c>
       <c r="U9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V9" t="n">
         <v>1200</v>
@@ -1404,10 +1404,10 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="V10" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>139.7</v>
       </c>
       <c r="U11" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="V11" t="n">
         <v>600</v>
@@ -1683,7 +1683,7 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V13" t="n">
         <v>350</v>
@@ -1776,7 +1776,7 @@
         <v>141</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
         <v>200</v>
@@ -1869,7 +1869,7 @@
         <v>141</v>
       </c>
       <c r="U15" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="V15" t="n">
         <v>350</v>
@@ -1962,7 +1962,7 @@
         <v>48.5</v>
       </c>
       <c r="U16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V16" t="n">
         <v>1000</v>
@@ -2055,7 +2055,7 @@
         <v>31.8</v>
       </c>
       <c r="U17" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="V17" t="n">
         <v>300</v>
@@ -2148,10 +2148,10 @@
         <v>59.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>600</v>
+        <v>23040</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>60.2</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
         <v>3500</v>
@@ -2334,7 +2334,7 @@
         <v>59.2</v>
       </c>
       <c r="U20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V20" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="V21" t="n">
         <v>600</v>
@@ -2520,7 +2520,7 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="V22" t="n">
         <v>600</v>
@@ -2613,10 +2613,10 @@
         <v>59.2</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V23" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>141</v>
       </c>
       <c r="U24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
         <v>200</v>
@@ -2799,10 +2799,10 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="V25" t="n">
-        <v>950</v>
+        <v>450</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>98.2</v>
       </c>
       <c r="U26" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="V26" t="n">
         <v>800</v>
@@ -3264,9 +3264,11 @@
         <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>10000</v>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3355,7 +3357,7 @@
         <v>122.7</v>
       </c>
       <c r="U31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V31" t="n">
         <v>500</v>
@@ -3634,7 +3636,7 @@
         <v>98.2</v>
       </c>
       <c r="U34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V34" t="n">
         <v>10</v>
@@ -3727,7 +3729,7 @@
         <v>141</v>
       </c>
       <c r="U35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V35" t="n">
         <v>200</v>
@@ -3820,10 +3822,10 @@
         <v>98.2</v>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V36" t="n">
-        <v>4199</v>
+        <v>700</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -3913,10 +3915,10 @@
         <v>59.2</v>
       </c>
       <c r="U37" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="V37" t="n">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4006,7 +4008,7 @@
         <v>59.2</v>
       </c>
       <c r="U38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V38" t="n">
         <v>10</v>
@@ -4099,7 +4101,7 @@
         <v>139.7</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
@@ -4190,7 +4192,7 @@
         <v>47.6</v>
       </c>
       <c r="U40" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V40" t="n">
         <v>200</v>
@@ -4465,7 +4467,7 @@
         <v>31.8</v>
       </c>
       <c r="U43" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="V43" t="n">
         <v>300</v>
@@ -4558,10 +4560,10 @@
         <v>28.3</v>
       </c>
       <c r="U44" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="V44" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -4651,10 +4653,10 @@
         <v>60.2</v>
       </c>
       <c r="U45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
-        <v>1200</v>
+        <v>3500</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -4930,7 +4932,7 @@
         <v>28.3</v>
       </c>
       <c r="U48" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V48" t="n">
         <v>600</v>
@@ -5023,7 +5025,7 @@
         <v>60.2</v>
       </c>
       <c r="U49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V49" t="n">
         <v>100</v>
@@ -5116,7 +5118,7 @@
         <v>28.3</v>
       </c>
       <c r="U50" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="V50" t="n">
         <v>500</v>
@@ -5209,7 +5211,7 @@
         <v>59.2</v>
       </c>
       <c r="U51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V51" t="n">
         <v>10</v>
@@ -5302,7 +5304,7 @@
         <v>31.8</v>
       </c>
       <c r="U52" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V52" t="n">
         <v>300</v>
@@ -5395,7 +5397,7 @@
         <v>59.2</v>
       </c>
       <c r="U53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V53" t="n">
         <v>6000</v>
@@ -5488,9 +5490,11 @@
         <v>184.9</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V54" t="n">
+        <v>3900</v>
+      </c>
       <c r="W54" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5579,7 +5583,7 @@
         <v>28.3</v>
       </c>
       <c r="U55" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V55" t="n">
         <v>600</v>
@@ -5765,7 +5769,7 @@
         <v>59.2</v>
       </c>
       <c r="U57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
@@ -5856,10 +5860,10 @@
         <v>122.7</v>
       </c>
       <c r="U58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V58" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -5949,10 +5953,10 @@
         <v>122.7</v>
       </c>
       <c r="U59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V59" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -6321,10 +6325,10 @@
         <v>213.9</v>
       </c>
       <c r="U63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V63" t="n">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6414,10 +6418,10 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V64" t="n">
-        <v>200</v>
+        <v>1800</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -6507,10 +6511,10 @@
         <v>184.9</v>
       </c>
       <c r="U65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V65" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -6600,7 +6604,7 @@
         <v>184.9</v>
       </c>
       <c r="U66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V66" t="n">
         <v>500</v>
@@ -6789,7 +6793,7 @@
         <v>11</v>
       </c>
       <c r="V68" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -7063,10 +7067,10 @@
         <v>270.6</v>
       </c>
       <c r="U71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V71" t="n">
-        <v>6000</v>
+        <v>1925</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
@@ -7247,9 +7251,11 @@
         <v>184.9</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
-      </c>
-      <c r="V73" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V73" t="n">
+        <v>3900</v>
+      </c>
       <c r="W73" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7431,7 +7437,7 @@
         <v>270.6</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
@@ -7613,10 +7619,10 @@
         <v>213.9</v>
       </c>
       <c r="U77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V77" t="n">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="W77" t="inlineStr">
         <is>
@@ -7706,9 +7712,11 @@
         <v>270.6</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1925</v>
+      </c>
       <c r="W78" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8072,10 +8080,10 @@
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V82" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -8438,9 +8446,11 @@
         <v>270.6</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V86" t="n">
+        <v>1925</v>
+      </c>
       <c r="W86" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9985,11 +9995,9 @@
         <v>184.9</v>
       </c>
       <c r="U103" t="n">
-        <v>1</v>
-      </c>
-      <c r="V103" t="n">
-        <v>600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10444,9 +10452,11 @@
         <v>129.6</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V108" t="n">
+        <v>300</v>
+      </c>
       <c r="W108" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -11629,11 +11639,9 @@
         <v>147.5</v>
       </c>
       <c r="U121" t="n">
-        <v>1</v>
-      </c>
-      <c r="V121" t="n">
-        <v>1600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V121" t="inlineStr"/>
       <c r="W121" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -11813,9 +11821,11 @@
         <v>37.9</v>
       </c>
       <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V123" t="n">
+        <v>350</v>
+      </c>
       <c r="W123" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -12177,11 +12187,9 @@
         <v>147.5</v>
       </c>
       <c r="U127" t="n">
-        <v>1</v>
-      </c>
-      <c r="V127" t="n">
-        <v>1600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr">
         <is>
           <t>рекомендуемая</t>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="V2" t="n">
         <v>200</v>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="V3" t="n">
         <v>300</v>
@@ -939,7 +939,7 @@
         <v>28.3</v>
       </c>
       <c r="U5" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="V5" t="n">
         <v>500</v>
@@ -1032,7 +1032,7 @@
         <v>141</v>
       </c>
       <c r="U6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6" t="n">
         <v>1000</v>
@@ -1125,7 +1125,7 @@
         <v>141</v>
       </c>
       <c r="U7" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="V7" t="n">
         <v>300</v>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V8" t="n">
         <v>900</v>
@@ -1311,7 +1311,7 @@
         <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="V9" t="n">
         <v>600</v>
@@ -1404,7 +1404,7 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="V10" t="n">
         <v>950</v>
@@ -1590,7 +1590,7 @@
         <v>59.2</v>
       </c>
       <c r="U12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="V12" t="n">
         <v>10</v>
@@ -1683,7 +1683,7 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
         <v>1000</v>
@@ -1776,7 +1776,7 @@
         <v>98.2</v>
       </c>
       <c r="U14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V14" t="n">
         <v>350</v>
@@ -1869,7 +1869,7 @@
         <v>141</v>
       </c>
       <c r="U15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V15" t="n">
         <v>200</v>
@@ -1962,7 +1962,7 @@
         <v>141</v>
       </c>
       <c r="U16" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="V16" t="n">
         <v>350</v>
@@ -1996,19 +1996,19 @@
         <v>87</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>41.282312</v>
+        <v>41.284507</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>69.355769</v>
+        <v>69.237188</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.282312, 69.355769</t>
+          <t>41.284507, 69.237188</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Авиасозлар-1</t>
+          <t>Ракат махалля</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2017,30 +2017,30 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>17265</v>
+        <v>7882</v>
       </c>
       <c r="M17" t="n">
         <v>7</v>
       </c>
       <c r="N17" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="P17" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="Q17" t="n">
         <v>0.5</v>
@@ -2049,16 +2049,16 @@
         <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>480</v>
+        <v>312</v>
       </c>
       <c r="T17" t="n">
-        <v>141</v>
+        <v>31.8</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>121</v>
       </c>
       <c r="V17" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.282312,69.355769</t>
+          <t>https://www.google.com/maps?q=41.284507,69.237188</t>
         </is>
       </c>
     </row>
@@ -2089,19 +2089,19 @@
         <v>87</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>41.284507</v>
+        <v>41.282312</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>69.237188</v>
+        <v>69.355769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.284507, 69.237188</t>
+          <t>41.282312, 69.355769</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ракат махалля</t>
+          <t>Авиасозлар-1</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2110,30 +2110,30 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>7882</v>
+        <v>17265</v>
       </c>
       <c r="M18" t="n">
         <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="Q18" t="n">
         <v>0.5</v>
@@ -2142,16 +2142,16 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>312</v>
+        <v>480</v>
       </c>
       <c r="T18" t="n">
-        <v>31.8</v>
+        <v>141</v>
       </c>
       <c r="U18" t="n">
-        <v>121</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.284507,69.237188</t>
+          <t>https://www.google.com/maps?q=41.282312,69.355769</t>
         </is>
       </c>
     </row>
@@ -2334,9 +2334,11 @@
         <v>60.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1872</v>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -2425,7 +2427,7 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="V21" t="n">
         <v>600</v>
@@ -2459,19 +2461,19 @@
         <v>83</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>41.260613</v>
+        <v>41.355449</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>69.327422</v>
+        <v>69.286761</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.260613, 69.327422</t>
+          <t>41.355449, 69.286761</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Бунёдкор махалля</t>
+          <t>Юнусабад-1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2480,48 +2482,48 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3292</v>
+        <v>10097</v>
       </c>
       <c r="M22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="Q22" t="n">
         <v>0.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>141</v>
+        <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="V22" t="n">
-        <v>1400</v>
+        <v>950</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2535,7 +2537,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.260613,69.327422</t>
+          <t>https://www.google.com/maps?q=41.355449,69.286761</t>
         </is>
       </c>
     </row>
@@ -2552,19 +2554,19 @@
         <v>83</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>41.355449</v>
+        <v>41.260613</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>69.286761</v>
+        <v>69.327422</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.355449, 69.286761</t>
+          <t>41.260613, 69.327422</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Юнусабад-1</t>
+          <t>Бунёдкор махалля</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2573,48 +2575,48 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>10097</v>
+        <v>3292</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N23" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="Q23" t="n">
         <v>0.5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="T23" t="n">
-        <v>139.7</v>
+        <v>141</v>
       </c>
       <c r="U23" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>950</v>
+        <v>1400</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2628,7 +2630,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.355449,69.286761</t>
+          <t>https://www.google.com/maps?q=41.260613,69.327422</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2799,7 @@
         <v>28.3</v>
       </c>
       <c r="U25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V25" t="n">
         <v>350</v>
@@ -2890,7 +2892,7 @@
         <v>139.7</v>
       </c>
       <c r="U26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V26" t="n">
         <v>950</v>
@@ -2983,10 +2985,10 @@
         <v>98.2</v>
       </c>
       <c r="U27" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="V27" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3017,19 +3019,19 @@
         <v>80</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>41.272355</v>
+        <v>41.318137</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>69.339643</v>
+        <v>69.360837</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>41.272355, 69.339643</t>
+          <t>41.318137, 69.360837</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Хосиятли махалля</t>
+          <t>Гульзарабад махалля</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3038,7 +3040,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3049,19 +3051,19 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>7321</v>
+        <v>7413</v>
       </c>
       <c r="M28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="O28" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="Q28" t="n">
         <v>0.5</v>
@@ -3076,10 +3078,10 @@
         <v>141</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3093,7 +3095,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.272355,69.339643</t>
+          <t>https://www.google.com/maps?q=41.318137,69.360837</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3171,7 @@
         <v>139.7</v>
       </c>
       <c r="U29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V29" t="n">
         <v>900</v>
@@ -3203,19 +3205,19 @@
         <v>80</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>41.319771</v>
+        <v>41.272355</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>69.364845</v>
+        <v>69.339643</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>41.319771, 69.364845</t>
+          <t>41.272355, 69.339643</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Гульзарабад махалля</t>
+          <t>Хосиятли махалля</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3224,7 +3226,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3235,19 +3237,19 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>8138</v>
+        <v>7321</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N30" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="O30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P30" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="Q30" t="n">
         <v>0.5</v>
@@ -3262,11 +3264,9 @@
         <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.319771,69.364845</t>
+          <t>https://www.google.com/maps?q=41.272355,69.339643</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3355,7 @@
         <v>122.7</v>
       </c>
       <c r="U31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V31" t="n">
         <v>500</v>
@@ -3541,10 +3541,10 @@
         <v>141</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>1200</v>
+        <v>1872</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>98.2</v>
       </c>
       <c r="U34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V34" t="n">
         <v>4199</v>
@@ -3820,7 +3820,7 @@
         <v>47.6</v>
       </c>
       <c r="U36" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="V36" t="n">
         <v>200</v>
@@ -3913,7 +3913,7 @@
         <v>139.7</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
@@ -4279,7 +4279,7 @@
         <v>28.3</v>
       </c>
       <c r="U41" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="V41" t="n">
         <v>250</v>
@@ -4372,7 +4372,7 @@
         <v>28.3</v>
       </c>
       <c r="U42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V42" t="n">
         <v>600</v>
@@ -4465,7 +4465,7 @@
         <v>59.2</v>
       </c>
       <c r="U43" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="V43" t="n">
         <v>450</v>
@@ -4558,7 +4558,7 @@
         <v>48.5</v>
       </c>
       <c r="U44" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="V44" t="n">
         <v>300</v>
@@ -4744,7 +4744,7 @@
         <v>28.3</v>
       </c>
       <c r="U46" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="V46" t="n">
         <v>500</v>
@@ -4837,7 +4837,7 @@
         <v>31.8</v>
       </c>
       <c r="U47" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="V47" t="n">
         <v>300</v>
@@ -4930,11 +4930,9 @@
         <v>60.2</v>
       </c>
       <c r="U48" t="n">
-        <v>5</v>
-      </c>
-      <c r="V48" t="n">
-        <v>100</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5116,10 +5114,10 @@
         <v>59.2</v>
       </c>
       <c r="U50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V50" t="n">
-        <v>6000</v>
+        <v>23040</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5305,7 +5303,7 @@
         <v>1</v>
       </c>
       <c r="V52" t="n">
-        <v>3900</v>
+        <v>500</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -5488,7 +5486,7 @@
         <v>139.7</v>
       </c>
       <c r="U54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V54" t="n">
         <v>6000</v>
@@ -5581,7 +5579,7 @@
         <v>122.7</v>
       </c>
       <c r="U55" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V55" t="n">
         <v>130</v>
@@ -5674,7 +5672,7 @@
         <v>28.3</v>
       </c>
       <c r="U56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V56" t="n">
         <v>350</v>
@@ -5860,11 +5858,9 @@
         <v>60.2</v>
       </c>
       <c r="U58" t="n">
-        <v>4</v>
-      </c>
-      <c r="V58" t="n">
-        <v>100</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6046,7 +6042,7 @@
         <v>122.7</v>
       </c>
       <c r="U60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V60" t="n">
         <v>130</v>
@@ -6077,7 +6073,7 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>41.240681</v>
@@ -6323,10 +6319,10 @@
         <v>184.9</v>
       </c>
       <c r="U63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V63" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6351,7 +6347,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C64" t="n">
         <v>87</v>
@@ -6419,7 +6415,7 @@
         <v>8</v>
       </c>
       <c r="V64" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -6509,10 +6505,10 @@
         <v>184.9</v>
       </c>
       <c r="U65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V65" t="n">
-        <v>6000</v>
+        <v>250</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -6695,7 +6691,7 @@
         <v>270.6</v>
       </c>
       <c r="U67" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V67" t="n">
         <v>1000</v>
@@ -6788,7 +6784,7 @@
         <v>270.6</v>
       </c>
       <c r="U68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V68" t="n">
         <v>900</v>
@@ -6881,7 +6877,7 @@
         <v>270.6</v>
       </c>
       <c r="U69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V69" t="n">
         <v>1925</v>
@@ -6974,9 +6970,11 @@
         <v>270.6</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V70" t="n">
+        <v>250</v>
+      </c>
       <c r="W70" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7156,7 +7154,7 @@
         <v>270.6</v>
       </c>
       <c r="U72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V72" t="n">
         <v>1925</v>
@@ -7249,7 +7247,7 @@
         <v>270.6</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
@@ -7797,11 +7795,9 @@
         <v>213.9</v>
       </c>
       <c r="U79" t="n">
-        <v>1</v>
-      </c>
-      <c r="V79" t="n">
-        <v>1000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7890,9 +7886,11 @@
         <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V80" t="n">
+        <v>1100</v>
+      </c>
       <c r="W80" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7916,7 +7914,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C81" t="n">
         <v>87</v>
@@ -8740,7 +8738,7 @@
         <v>58</v>
       </c>
       <c r="C90" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>41.389799</v>
@@ -8802,9 +8800,11 @@
         <v>213.9</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V90" t="n">
+        <v>1100</v>
+      </c>
       <c r="W90" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10262,10 +10262,10 @@
         <v>40.8</v>
       </c>
       <c r="U106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V106" t="n">
-        <v>700</v>
+        <v>2000</v>
       </c>
       <c r="W106" t="inlineStr">
         <is>
@@ -10539,10 +10539,10 @@
         <v>40.8</v>
       </c>
       <c r="U109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V109" t="n">
-        <v>700</v>
+        <v>2000</v>
       </c>
       <c r="W109" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>41</v>
       </c>
       <c r="C117" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>41.135856</v>
@@ -14216,7 +14216,7 @@
         <v>26</v>
       </c>
       <c r="C150" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>40.804571</v>
@@ -15217,7 +15217,7 @@
         <v>41</v>
       </c>
       <c r="C161" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>40.954123</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="V2" t="n">
         <v>200</v>
@@ -753,10 +753,10 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V3" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V4" t="n">
         <v>1000</v>
@@ -939,7 +939,7 @@
         <v>122.7</v>
       </c>
       <c r="U5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="V5" t="n">
         <v>130</v>
@@ -1032,7 +1032,7 @@
         <v>28.3</v>
       </c>
       <c r="U6" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="V6" t="n">
         <v>500</v>
@@ -1125,7 +1125,7 @@
         <v>141</v>
       </c>
       <c r="U7" t="n">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="V7" t="n">
         <v>300</v>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="V8" t="n">
         <v>350</v>
@@ -1314,7 +1314,7 @@
         <v>15</v>
       </c>
       <c r="V9" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V10" t="n">
         <v>600</v>
@@ -1590,7 +1590,7 @@
         <v>98.2</v>
       </c>
       <c r="U12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V12" t="n">
         <v>800</v>
@@ -1683,7 +1683,7 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V13" t="n">
         <v>1000</v>
@@ -1776,10 +1776,10 @@
         <v>141</v>
       </c>
       <c r="U14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="V14" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
         <v>98.2</v>
       </c>
       <c r="U15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V15" t="n">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1903,19 +1903,19 @@
         <v>88</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>41.282312</v>
+        <v>41.284507</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>69.355769</v>
+        <v>69.237188</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.282312, 69.355769</t>
+          <t>41.284507, 69.237188</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Авиасозлар-1</t>
+          <t>Ракат махалля</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1924,30 +1924,30 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>17265</v>
+        <v>7882</v>
       </c>
       <c r="M16" t="n">
         <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="P16" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="Q16" t="n">
         <v>0.5</v>
@@ -1956,16 +1956,16 @@
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>480</v>
+        <v>312</v>
       </c>
       <c r="T16" t="n">
-        <v>141</v>
+        <v>31.8</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="V16" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.282312,69.355769</t>
+          <t>https://www.google.com/maps?q=41.284507,69.237188</t>
         </is>
       </c>
     </row>
@@ -1996,19 +1996,19 @@
         <v>87</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>41.284507</v>
+        <v>41.283946</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>69.237188</v>
+        <v>69.359775</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.284507, 69.237188</t>
+          <t>41.283946, 69.359775</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ракат махалля</t>
+          <t>Авиасозлар-1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2017,30 +2017,30 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>7882</v>
+        <v>13526</v>
       </c>
       <c r="M17" t="n">
         <v>7</v>
       </c>
       <c r="N17" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="O17" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="Q17" t="n">
         <v>0.5</v>
@@ -2049,13 +2049,13 @@
         <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>312</v>
+        <v>480</v>
       </c>
       <c r="T17" t="n">
-        <v>31.8</v>
+        <v>141</v>
       </c>
       <c r="U17" t="n">
-        <v>124</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
         <v>200</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.284507,69.237188</t>
+          <t>https://www.google.com/maps?q=41.283946,69.359775</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
         <v>48.5</v>
       </c>
       <c r="U18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
         <v>1000</v>
@@ -2334,10 +2334,10 @@
         <v>98.2</v>
       </c>
       <c r="U20" t="n">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="V20" t="n">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="V21" t="n">
         <v>450</v>
@@ -2613,10 +2613,10 @@
         <v>139.7</v>
       </c>
       <c r="U23" t="n">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="V23" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>41.355449</v>
@@ -2706,7 +2706,7 @@
         <v>139.7</v>
       </c>
       <c r="U24" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="V24" t="n">
         <v>350</v>
@@ -2799,10 +2799,10 @@
         <v>28.3</v>
       </c>
       <c r="U25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V25" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="V27" t="n">
         <v>350</v>
@@ -3078,7 +3078,7 @@
         <v>141</v>
       </c>
       <c r="U28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V28" t="n">
         <v>200</v>
@@ -3171,10 +3171,10 @@
         <v>139.7</v>
       </c>
       <c r="U29" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="V29" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3264,10 +3264,10 @@
         <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1100</v>
+        <v>2600</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>122.7</v>
       </c>
       <c r="U31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31" t="n">
         <v>500</v>
@@ -3543,10 +3543,10 @@
         <v>122.7</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V33" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>98.2</v>
       </c>
       <c r="U34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
         <v>3876</v>
@@ -3729,7 +3729,7 @@
         <v>98.2</v>
       </c>
       <c r="U35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V35" t="n">
         <v>10</v>
@@ -3822,7 +3822,7 @@
         <v>59.2</v>
       </c>
       <c r="U36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V36" t="n">
         <v>250</v>
@@ -3915,7 +3915,7 @@
         <v>47.6</v>
       </c>
       <c r="U37" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="V37" t="n">
         <v>200</v>
@@ -4008,11 +4008,9 @@
         <v>139.7</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1200</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4192,7 +4190,7 @@
         <v>31.8</v>
       </c>
       <c r="U40" t="n">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="V40" t="n">
         <v>300</v>
@@ -4285,7 +4283,7 @@
         <v>28.3</v>
       </c>
       <c r="U41" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="V41" t="n">
         <v>250</v>
@@ -4378,7 +4376,7 @@
         <v>47.6</v>
       </c>
       <c r="U42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V42" t="n">
         <v>200</v>
@@ -4564,7 +4562,7 @@
         <v>28.3</v>
       </c>
       <c r="U44" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="V44" t="n">
         <v>600</v>
@@ -4657,7 +4655,7 @@
         <v>48.5</v>
       </c>
       <c r="U45" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="V45" t="n">
         <v>300</v>
@@ -4843,7 +4841,7 @@
         <v>28.3</v>
       </c>
       <c r="U47" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="V47" t="n">
         <v>500</v>
@@ -5029,7 +5027,7 @@
         <v>48.5</v>
       </c>
       <c r="U49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V49" t="n">
         <v>1200</v>
@@ -5122,10 +5120,10 @@
         <v>31.8</v>
       </c>
       <c r="U50" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="V50" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5215,7 +5213,7 @@
         <v>47.6</v>
       </c>
       <c r="U51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V51" t="n">
         <v>500</v>
@@ -5308,7 +5306,7 @@
         <v>122.7</v>
       </c>
       <c r="U52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V52" t="n">
         <v>130</v>
@@ -5401,10 +5399,10 @@
         <v>28.3</v>
       </c>
       <c r="U53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V53" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -5773,7 +5771,7 @@
         <v>122.7</v>
       </c>
       <c r="U57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V57" t="n">
         <v>130</v>
@@ -5897,7 +5895,7 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>41.240681</v>
@@ -6050,7 +6048,7 @@
         <v>139.7</v>
       </c>
       <c r="U60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V60" t="n">
         <v>6000</v>
@@ -6081,7 +6079,7 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>41.316603</v>
@@ -6234,10 +6232,10 @@
         <v>213.9</v>
       </c>
       <c r="U62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V62" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -6327,10 +6325,10 @@
         <v>270.6</v>
       </c>
       <c r="U63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V63" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6420,9 +6418,11 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>250</v>
+      </c>
       <c r="W64" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6511,10 +6511,10 @@
         <v>270.6</v>
       </c>
       <c r="U65" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V65" t="n">
-        <v>1300</v>
+        <v>100</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>184.9</v>
       </c>
       <c r="U66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V66" t="n">
         <v>200</v>
@@ -6791,7 +6791,7 @@
         <v>3</v>
       </c>
       <c r="V68" t="n">
-        <v>1925</v>
+        <v>15120</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -6972,9 +6972,11 @@
         <v>184.9</v>
       </c>
       <c r="U70" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V70" t="n">
+        <v>3900</v>
+      </c>
       <c r="W70" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -7154,10 +7156,10 @@
         <v>270.6</v>
       </c>
       <c r="U72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V72" t="n">
-        <v>1925</v>
+        <v>6000</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
@@ -7247,7 +7249,7 @@
         <v>270.6</v>
       </c>
       <c r="U73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
@@ -7613,9 +7615,11 @@
         <v>270.6</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V77" t="n">
+        <v>250</v>
+      </c>
       <c r="W77" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8070,11 +8074,9 @@
         <v>270.6</v>
       </c>
       <c r="U82" t="n">
-        <v>1</v>
-      </c>
-      <c r="V82" t="n">
-        <v>1925</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9077,9 +9079,11 @@
         <v>184.9</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V93" t="n">
+        <v>1120</v>
+      </c>
       <c r="W93" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10111,7 +10115,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>41.45833</v>
@@ -10446,10 +10450,10 @@
         <v>40.8</v>
       </c>
       <c r="U108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V108" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="W108" t="inlineStr">
         <is>
@@ -11631,11 +11635,9 @@
         <v>147.5</v>
       </c>
       <c r="U121" t="n">
-        <v>1</v>
-      </c>
-      <c r="V121" t="n">
-        <v>1600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V121" t="inlineStr"/>
       <c r="W121" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -12090,11 +12092,9 @@
         <v>147.5</v>
       </c>
       <c r="U126" t="n">
-        <v>1</v>
-      </c>
-      <c r="V126" t="n">
-        <v>1600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13665,7 +13665,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C144" t="n">
         <v>51</v>
@@ -13850,7 +13850,7 @@
         <v>10</v>
       </c>
       <c r="C146" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>40.834346</v>
@@ -15576,7 +15576,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C165" t="n">
         <v>51</v>
@@ -16944,7 +16944,7 @@
         <v>6</v>
       </c>
       <c r="C180" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>41.61707</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V2" t="n">
         <v>200</v>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V3" t="n">
         <v>200</v>
@@ -846,7 +846,7 @@
         <v>28.3</v>
       </c>
       <c r="U4" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="V4" t="n">
         <v>450</v>
@@ -942,7 +942,7 @@
         <v>11</v>
       </c>
       <c r="V5" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>141</v>
       </c>
       <c r="U6" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="V6" t="n">
         <v>300</v>
@@ -1125,7 +1125,7 @@
         <v>48.5</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
         <v>1000</v>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="V8" t="n">
         <v>350</v>
@@ -1497,7 +1497,7 @@
         <v>59.2</v>
       </c>
       <c r="U11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V11" t="n">
         <v>10</v>
@@ -1590,7 +1590,7 @@
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="V12" t="n">
         <v>300</v>
@@ -1683,7 +1683,7 @@
         <v>141</v>
       </c>
       <c r="U13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V13" t="n">
         <v>350</v>
@@ -1776,7 +1776,7 @@
         <v>98.2</v>
       </c>
       <c r="U14" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="V14" t="n">
         <v>800</v>
@@ -1869,7 +1869,7 @@
         <v>98.2</v>
       </c>
       <c r="U15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V15" t="n">
         <v>1000</v>
@@ -1938,7 +1938,7 @@
         <v>9976</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
         <v>31</v>
@@ -1962,7 +1962,7 @@
         <v>98.2</v>
       </c>
       <c r="U16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V16" t="n">
         <v>350</v>
@@ -2055,7 +2055,7 @@
         <v>31.8</v>
       </c>
       <c r="U17" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="V17" t="n">
         <v>200</v>
@@ -2148,7 +2148,7 @@
         <v>98.2</v>
       </c>
       <c r="U18" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="V18" t="n">
         <v>350</v>
@@ -2217,7 +2217,7 @@
         <v>13526</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
         <v>9</v>
@@ -2241,10 +2241,10 @@
         <v>141</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="V22" t="n">
         <v>600</v>
@@ -2706,7 +2706,7 @@
         <v>59.2</v>
       </c>
       <c r="U24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V24" t="n">
         <v>200</v>
@@ -2892,7 +2892,7 @@
         <v>139.7</v>
       </c>
       <c r="U26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="V26" t="n">
         <v>450</v>
@@ -2985,7 +2985,7 @@
         <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="V27" t="n">
         <v>350</v>
@@ -3078,10 +3078,10 @@
         <v>28.3</v>
       </c>
       <c r="U28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V28" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
         <v>141</v>
       </c>
       <c r="U29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V29" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3205,19 +3205,19 @@
         <v>81</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>41.318137</v>
+        <v>41.384298</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>69.360837</v>
+        <v>69.29950700000001</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>41.318137, 69.360837</t>
+          <t>41.384298, 69.299507</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Гульзарабад махалля</t>
+          <t>Орзулар</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3226,30 +3226,30 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>7413</v>
+        <v>9262</v>
       </c>
       <c r="M30" t="n">
         <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="O30" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="P30" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="Q30" t="n">
         <v>0.5</v>
@@ -3261,13 +3261,13 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>141</v>
+        <v>139.7</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="V30" t="n">
-        <v>1100</v>
+        <v>600</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.318137,69.360837</t>
+          <t>https://www.google.com/maps?q=41.384298,69.299507</t>
         </is>
       </c>
     </row>
@@ -3298,19 +3298,19 @@
         <v>81</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>41.384298</v>
+        <v>41.318137</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>69.29950700000001</v>
+        <v>69.360837</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>41.384298, 69.299507</t>
+          <t>41.318137, 69.360837</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Орзулар</t>
+          <t>Гульзарабад махалля</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3319,30 +3319,30 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>9262</v>
+        <v>7413</v>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P31" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="Q31" t="n">
         <v>0.5</v>
@@ -3354,13 +3354,13 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>139.7</v>
+        <v>141</v>
       </c>
       <c r="U31" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="V31" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.384298,69.299507</t>
+          <t>https://www.google.com/maps?q=41.318137,69.360837</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
         <v>141</v>
       </c>
       <c r="U34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V34" t="n">
         <v>10</v>
@@ -3729,10 +3729,10 @@
         <v>122.7</v>
       </c>
       <c r="U35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V35" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>98.2</v>
       </c>
       <c r="U37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
         <v>10</v>
@@ -4008,11 +4008,9 @@
         <v>184.9</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" t="n">
-        <v>250</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4101,7 +4099,7 @@
         <v>98.2</v>
       </c>
       <c r="U39" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="V39" t="n">
         <v>350</v>
@@ -4194,7 +4192,7 @@
         <v>59.2</v>
       </c>
       <c r="U40" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="V40" t="n">
         <v>250</v>
@@ -4228,69 +4226,69 @@
         <v>78</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>41.286991</v>
+        <v>41.389937</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>69.19375700000001</v>
+        <v>69.27194299999999</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>41.286991, 69.193757</t>
+          <t>41.389937, 69.271943</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Чиланзар Г 9А</t>
+          <t>Бешкурган</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>16603</v>
+        <v>1877</v>
       </c>
       <c r="M41" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="O41" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="P41" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="Q41" t="n">
         <v>0.5</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="T41" t="n">
-        <v>47.6</v>
+        <v>139.7</v>
       </c>
       <c r="U41" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4304,7 +4302,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
+          <t>https://www.google.com/maps?q=41.389937,69.271943</t>
         </is>
       </c>
     </row>
@@ -4321,69 +4319,69 @@
         <v>78</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>41.389937</v>
+        <v>41.286991</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>69.27194299999999</v>
+        <v>69.19375700000001</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>41.389937, 69.271943</t>
+          <t>41.286991, 69.193757</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Бешкурган</t>
+          <t>Чиланзар Г 9А</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1877</v>
+        <v>16603</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N42" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="O42" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="P42" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="Q42" t="n">
         <v>0.5</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>139.7</v>
+        <v>47.6</v>
       </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="V42" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4397,7 +4395,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.389937,69.271943</t>
+          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4471,7 @@
         <v>98.2</v>
       </c>
       <c r="U43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V43" t="n">
         <v>10</v>
@@ -4748,7 +4746,7 @@
         <v>31.8</v>
       </c>
       <c r="U46" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="V46" t="n">
         <v>300</v>
@@ -4841,7 +4839,7 @@
         <v>28.3</v>
       </c>
       <c r="U47" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="V47" t="n">
         <v>250</v>
@@ -4934,7 +4932,7 @@
         <v>139.7</v>
       </c>
       <c r="U48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V48" t="n">
         <v>100</v>
@@ -5213,7 +5211,7 @@
         <v>48.5</v>
       </c>
       <c r="U51" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="V51" t="n">
         <v>300</v>
@@ -5306,7 +5304,7 @@
         <v>28.3</v>
       </c>
       <c r="U52" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V52" t="n">
         <v>450</v>
@@ -5492,7 +5490,7 @@
         <v>31.8</v>
       </c>
       <c r="U54" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="V54" t="n">
         <v>200</v>
@@ -5678,7 +5676,7 @@
         <v>59.2</v>
       </c>
       <c r="U56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V56" t="n">
         <v>23040</v>
@@ -5957,7 +5955,7 @@
         <v>139.7</v>
       </c>
       <c r="U59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V59" t="n">
         <v>6000</v>
@@ -6050,10 +6048,10 @@
         <v>122.7</v>
       </c>
       <c r="U60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V60" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6143,10 +6141,10 @@
         <v>122.7</v>
       </c>
       <c r="U61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V61" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -6329,7 +6327,7 @@
         <v>213.9</v>
       </c>
       <c r="U63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V63" t="n">
         <v>100</v>
@@ -6422,11 +6420,9 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>1</v>
-      </c>
-      <c r="V64" t="n">
-        <v>250</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6515,7 +6511,7 @@
         <v>213.9</v>
       </c>
       <c r="U65" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V65" t="n">
         <v>100</v>
@@ -6608,7 +6604,7 @@
         <v>270.6</v>
       </c>
       <c r="U66" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V66" t="n">
         <v>600</v>
@@ -6701,7 +6697,7 @@
         <v>270.6</v>
       </c>
       <c r="U67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V67" t="n">
         <v>100</v>
@@ -6794,7 +6790,7 @@
         <v>184.9</v>
       </c>
       <c r="U68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V68" t="n">
         <v>200</v>
@@ -6978,7 +6974,7 @@
         <v>270.6</v>
       </c>
       <c r="U70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
@@ -7069,7 +7065,7 @@
         <v>270.6</v>
       </c>
       <c r="U71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V71" t="n">
         <v>1925</v>
@@ -7344,7 +7340,7 @@
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V74" t="n">
         <v>1925</v>
@@ -8355,7 +8351,7 @@
         <v>184.9</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr">
@@ -10363,9 +10359,11 @@
         <v>40.8</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V107" t="n">
+        <v>2000</v>
+      </c>
       <c r="W107" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -11637,9 +11635,11 @@
         <v>147.5</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V121" t="n">
+        <v>1600</v>
+      </c>
       <c r="W121" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -12092,9 +12092,11 @@
         <v>147.5</v>
       </c>
       <c r="U126" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V126" t="n">
+        <v>1600</v>
+      </c>
       <c r="W126" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13216,42 +13218,42 @@
         <v>56</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>40.908494</v>
+        <v>40.869157</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>69.737362</v>
+        <v>69.040657</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>40.908494, 69.737362</t>
+          <t>40.869157, 69.040657</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Кара Китай</t>
+          <t>Аккурган</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
         <v>36.8</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Аккурганский район</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1955</v>
+        <v>3068</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
@@ -13260,7 +13262,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q139" t="n">
         <v>5</v>
@@ -13272,7 +13274,7 @@
         <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>55.2</v>
+        <v>40.3</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -13285,12 +13287,12 @@
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.908494,69.737362</t>
+          <t>https://www.google.com/maps?q=40.869157,69.040657</t>
         </is>
       </c>
     </row>
@@ -13307,42 +13309,42 @@
         <v>56</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>40.869157</v>
+        <v>40.908494</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>69.040657</v>
+        <v>69.737362</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>40.869157, 69.040657</t>
+          <t>40.908494, 69.737362</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Аккурган</t>
+          <t>Кара Китай</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J140" t="n">
         <v>36.8</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Аккурганский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>3068</v>
+        <v>1955</v>
       </c>
       <c r="M140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -13351,7 +13353,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
         <v>5</v>
@@ -13363,7 +13365,7 @@
         <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>40.3</v>
+        <v>55.2</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -13376,12 +13378,12 @@
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.869157,69.040657</t>
+          <t>https://www.google.com/maps?q=40.908494,69.737362</t>
         </is>
       </c>
     </row>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="V3" t="n">
         <v>200</v>
@@ -1032,7 +1032,7 @@
         <v>141</v>
       </c>
       <c r="U6" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="V6" t="n">
         <v>300</v>
@@ -1125,7 +1125,7 @@
         <v>48.5</v>
       </c>
       <c r="U7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
         <v>1000</v>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="V8" t="n">
         <v>350</v>
@@ -1311,10 +1311,10 @@
         <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V9" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V10" t="n">
         <v>600</v>
@@ -1590,7 +1590,7 @@
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="V12" t="n">
         <v>300</v>
@@ -1683,7 +1683,7 @@
         <v>141</v>
       </c>
       <c r="U13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="V13" t="n">
         <v>350</v>
@@ -1776,7 +1776,7 @@
         <v>98.2</v>
       </c>
       <c r="U14" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="V14" t="n">
         <v>800</v>
@@ -1869,7 +1869,7 @@
         <v>98.2</v>
       </c>
       <c r="U15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V15" t="n">
         <v>1000</v>
@@ -1938,7 +1938,7 @@
         <v>9976</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N16" t="n">
         <v>31</v>
@@ -2055,7 +2055,7 @@
         <v>31.8</v>
       </c>
       <c r="U17" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="V17" t="n">
         <v>200</v>
@@ -2148,7 +2148,7 @@
         <v>98.2</v>
       </c>
       <c r="U18" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="V18" t="n">
         <v>350</v>
@@ -2217,7 +2217,7 @@
         <v>13526</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
         <v>9</v>
@@ -2520,7 +2520,7 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="V22" t="n">
         <v>600</v>
@@ -2613,7 +2613,7 @@
         <v>139.7</v>
       </c>
       <c r="U23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V23" t="n">
         <v>350</v>
@@ -2706,7 +2706,7 @@
         <v>59.2</v>
       </c>
       <c r="U24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V24" t="n">
         <v>200</v>
@@ -2892,7 +2892,7 @@
         <v>139.7</v>
       </c>
       <c r="U26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V26" t="n">
         <v>450</v>
@@ -2985,7 +2985,7 @@
         <v>139.7</v>
       </c>
       <c r="U27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V27" t="n">
         <v>350</v>
@@ -3078,10 +3078,10 @@
         <v>28.3</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V28" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>141</v>
       </c>
       <c r="U29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V29" t="n">
         <v>200</v>
@@ -3205,19 +3205,19 @@
         <v>81</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>41.384298</v>
+        <v>41.318137</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>69.29950700000001</v>
+        <v>69.360837</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>41.384298, 69.299507</t>
+          <t>41.318137, 69.360837</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Орзулар</t>
+          <t>Гульзарабад махалля</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3226,30 +3226,30 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>9262</v>
+        <v>7413</v>
       </c>
       <c r="M30" t="n">
         <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P30" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="Q30" t="n">
         <v>0.5</v>
@@ -3261,13 +3261,13 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>139.7</v>
+        <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>600</v>
+        <v>1100</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.384298,69.299507</t>
+          <t>https://www.google.com/maps?q=41.318137,69.360837</t>
         </is>
       </c>
     </row>
@@ -3298,19 +3298,19 @@
         <v>81</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>41.318137</v>
+        <v>41.384298</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>69.360837</v>
+        <v>69.29950700000001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>41.318137, 69.360837</t>
+          <t>41.384298, 69.299507</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Гульзарабад махалля</t>
+          <t>Орзулар</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3319,30 +3319,30 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>7413</v>
+        <v>9262</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="O31" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="P31" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="Q31" t="n">
         <v>0.5</v>
@@ -3354,13 +3354,13 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>141</v>
+        <v>139.7</v>
       </c>
       <c r="U31" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="V31" t="n">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.318137,69.360837</t>
+          <t>https://www.google.com/maps?q=41.384298,69.299507</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
         <v>122.7</v>
       </c>
       <c r="U33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V33" t="n">
         <v>500</v>
@@ -3667,22 +3667,22 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>41.232153</v>
+        <v>41.325425</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>69.20011100000001</v>
+        <v>69.337316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>41.232153, 69.200111</t>
+          <t>41.325425, 69.337316</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Янги Чаштепа</t>
+          <t>Катта Алтынтепа махалля</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3691,48 +3691,48 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2145</v>
+        <v>9811</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="O35" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="P35" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q35" t="n">
         <v>0.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>122.7</v>
+        <v>98.2</v>
       </c>
       <c r="U35" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="V35" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.232153,69.200111</t>
+          <t>https://www.google.com/maps?q=41.325425,69.337316</t>
         </is>
       </c>
     </row>
@@ -3763,19 +3763,19 @@
         <v>79</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>41.250058</v>
+        <v>41.232153</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>69.342911</v>
+        <v>69.20011100000001</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>41.250058, 69.342911</t>
+          <t>41.232153, 69.200111</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Аханграбо (Панельный)</t>
+          <t>Янги Чаштепа</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3791,20 +3791,20 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Яшнободский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4446</v>
+        <v>2145</v>
       </c>
       <c r="M36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P36" t="n">
         <v>20</v>
@@ -3813,19 +3813,19 @@
         <v>0.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="T36" t="n">
-        <v>141</v>
+        <v>122.7</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V36" t="n">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.250058,69.342911</t>
+          <t>https://www.google.com/maps?q=41.232153,69.200111</t>
         </is>
       </c>
     </row>
@@ -3856,19 +3856,19 @@
         <v>79</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>41.346824</v>
+        <v>41.250058</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>69.38152599999999</v>
+        <v>69.342911</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>41.346824, 69.381526</t>
+          <t>41.250058, 69.342911</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ахмада Югнаки (Солнечный)</t>
+          <t>Аханграбо (Панельный)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3877,30 +3877,30 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Яшнободский район</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>10881</v>
+        <v>4446</v>
       </c>
       <c r="M37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N37" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="O37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P37" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="Q37" t="n">
         <v>0.5</v>
@@ -3912,13 +3912,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>98.2</v>
+        <v>141</v>
       </c>
       <c r="U37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
-        <v>10</v>
+        <v>1200</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.346824,69.381526</t>
+          <t>https://www.google.com/maps?q=41.250058,69.342911</t>
         </is>
       </c>
     </row>
@@ -3949,51 +3949,51 @@
         <v>79</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>41.359212</v>
+        <v>41.346824</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>69.172043</v>
+        <v>69.38152599999999</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>41.359212, 69.172043</t>
+          <t>41.346824, 69.381526</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Чигатай-Актепа</t>
+          <t>Ахмада Югнаки (Солнечный)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Мирзо Улугбекский район</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2530</v>
+        <v>10881</v>
       </c>
       <c r="M38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N38" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O38" t="n">
         <v>11</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q38" t="n">
         <v>0.5</v>
@@ -4005,12 +4005,14 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>184.9</v>
+        <v>98.2</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="V38" t="n">
+        <v>10</v>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4023,7 +4025,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.359212,69.172043</t>
+          <t>https://www.google.com/maps?q=41.346824,69.381526</t>
         </is>
       </c>
     </row>
@@ -4040,51 +4042,51 @@
         <v>79</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>41.323641</v>
+        <v>41.359212</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>69.341219</v>
+        <v>69.172043</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>41.323641, 69.341219</t>
+          <t>41.359212, 69.172043</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Катта Алтынтепа махалля</t>
+          <t>Чигатай-Актепа</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Мирзо Улугбекский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>6442</v>
+        <v>2530</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N39" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="O39" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="P39" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
         <v>0.5</v>
@@ -4096,13 +4098,13 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>98.2</v>
+        <v>184.9</v>
       </c>
       <c r="U39" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="V39" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4116,7 +4118,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.323641,69.341219</t>
+          <t>https://www.google.com/maps?q=41.359212,69.172043</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4194,7 @@
         <v>59.2</v>
       </c>
       <c r="U40" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V40" t="n">
         <v>250</v>
@@ -4226,69 +4228,69 @@
         <v>78</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>41.389937</v>
+        <v>41.286991</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>69.27194299999999</v>
+        <v>69.19375700000001</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>41.389937, 69.271943</t>
+          <t>41.286991, 69.193757</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Бешкурган</t>
+          <t>Чиланзар Г 9А</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Учтепинский район</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1877</v>
+        <v>16603</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N41" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="O41" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="P41" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="Q41" t="n">
         <v>0.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>139.7</v>
+        <v>47.6</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="V41" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4302,7 +4304,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.389937,69.271943</t>
+          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
         </is>
       </c>
     </row>
@@ -4319,69 +4321,69 @@
         <v>78</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>41.286991</v>
+        <v>41.389937</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>69.19375700000001</v>
+        <v>69.27194299999999</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>41.286991, 69.193757</t>
+          <t>41.389937, 69.271943</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Чиланзар Г 9А</t>
+          <t>Бешкурган</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Учтепинский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>16603</v>
+        <v>1877</v>
       </c>
       <c r="M42" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="O42" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="P42" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="Q42" t="n">
         <v>0.5</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="T42" t="n">
-        <v>47.6</v>
+        <v>139.7</v>
       </c>
       <c r="U42" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -4395,7 +4397,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.286991,69.193757</t>
+          <t>https://www.google.com/maps?q=41.389937,69.271943</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4411,7 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>41.342073</v>
@@ -4746,7 +4748,7 @@
         <v>31.8</v>
       </c>
       <c r="U46" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="V46" t="n">
         <v>300</v>
@@ -4839,7 +4841,7 @@
         <v>28.3</v>
       </c>
       <c r="U47" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="V47" t="n">
         <v>250</v>
@@ -4932,10 +4934,10 @@
         <v>139.7</v>
       </c>
       <c r="U48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V48" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -5025,7 +5027,7 @@
         <v>28.3</v>
       </c>
       <c r="U49" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V49" t="n">
         <v>450</v>
@@ -5211,7 +5213,7 @@
         <v>48.5</v>
       </c>
       <c r="U51" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="V51" t="n">
         <v>300</v>
@@ -5304,7 +5306,7 @@
         <v>28.3</v>
       </c>
       <c r="U52" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="V52" t="n">
         <v>450</v>
@@ -5397,10 +5399,10 @@
         <v>60.2</v>
       </c>
       <c r="U53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V53" t="n">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -5490,7 +5492,7 @@
         <v>31.8</v>
       </c>
       <c r="U54" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="V54" t="n">
         <v>200</v>
@@ -5676,7 +5678,7 @@
         <v>59.2</v>
       </c>
       <c r="U56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V56" t="n">
         <v>23040</v>
@@ -6048,7 +6050,7 @@
         <v>122.7</v>
       </c>
       <c r="U60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V60" t="n">
         <v>130</v>
@@ -6079,7 +6081,7 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>41.195341</v>
@@ -6141,7 +6143,7 @@
         <v>122.7</v>
       </c>
       <c r="U61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V61" t="n">
         <v>130</v>
@@ -6330,7 +6332,7 @@
         <v>6</v>
       </c>
       <c r="V63" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6420,9 +6422,11 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>250</v>
+      </c>
       <c r="W64" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -6511,10 +6515,10 @@
         <v>213.9</v>
       </c>
       <c r="U65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V65" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -6604,10 +6608,10 @@
         <v>270.6</v>
       </c>
       <c r="U66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V66" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -6697,10 +6701,10 @@
         <v>270.6</v>
       </c>
       <c r="U67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V67" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -6974,7 +6978,7 @@
         <v>270.6</v>
       </c>
       <c r="U70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
@@ -7065,10 +7069,10 @@
         <v>270.6</v>
       </c>
       <c r="U71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V71" t="n">
-        <v>1925</v>
+        <v>15120</v>
       </c>
       <c r="W71" t="inlineStr">
         <is>
@@ -7343,7 +7347,7 @@
         <v>4</v>
       </c>
       <c r="V74" t="n">
-        <v>1925</v>
+        <v>6000</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
@@ -8165,11 +8169,9 @@
         <v>270.6</v>
       </c>
       <c r="U83" t="n">
-        <v>1</v>
-      </c>
-      <c r="V83" t="n">
-        <v>1925</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -8351,7 +8353,7 @@
         <v>184.9</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr">
@@ -8744,7 +8746,7 @@
         <v>51</v>
       </c>
       <c r="C90" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>41.445931</v>
@@ -8925,7 +8927,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C92" t="n">
         <v>82</v>
@@ -9383,7 +9385,7 @@
         <v>26</v>
       </c>
       <c r="C97" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>41.408731</v>
@@ -9747,7 +9749,7 @@
         <v>40</v>
       </c>
       <c r="C101" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>41.445517</v>
@@ -10359,11 +10361,9 @@
         <v>40.8</v>
       </c>
       <c r="U107" t="n">
-        <v>1</v>
-      </c>
-      <c r="V107" t="n">
-        <v>2000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C111" t="n">
         <v>77</v>
@@ -10751,7 +10751,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C112" t="n">
         <v>82</v>
@@ -11388,7 +11388,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C119" t="n">
         <v>77</v>
@@ -13218,42 +13218,42 @@
         <v>56</v>
       </c>
       <c r="D139" s="2" t="n">
-        <v>40.869157</v>
+        <v>40.908494</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>69.040657</v>
+        <v>69.737362</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>40.869157, 69.040657</t>
+          <t>40.908494, 69.737362</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Аккурган</t>
+          <t>Кара Китай</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>город</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J139" t="n">
         <v>36.8</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Аккурганский район</t>
+          <t>Ахангаранский район</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>3068</v>
+        <v>1955</v>
       </c>
       <c r="M139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
@@ -13262,7 +13262,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
         <v>5</v>
@@ -13274,7 +13274,7 @@
         <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>40.3</v>
+        <v>55.2</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.869157,69.040657</t>
+          <t>https://www.google.com/maps?q=40.908494,69.737362</t>
         </is>
       </c>
     </row>
@@ -13309,42 +13309,42 @@
         <v>56</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>40.908494</v>
+        <v>40.869157</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>69.737362</v>
+        <v>69.040657</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>40.908494, 69.737362</t>
+          <t>40.869157, 69.040657</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Кара Китай</t>
+          <t>Аккурган</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>город</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J140" t="n">
         <v>36.8</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Ахангаранский район</t>
+          <t>Аккурганский район</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1955</v>
+        <v>3068</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -13353,7 +13353,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q140" t="n">
         <v>5</v>
@@ -13365,7 +13365,7 @@
         <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>55.2</v>
+        <v>40.3</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -13378,12 +13378,12 @@
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=40.908494,69.737362</t>
+          <t>https://www.google.com/maps?q=40.869157,69.040657</t>
         </is>
       </c>
     </row>
@@ -14759,7 +14759,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C156" t="n">
         <v>51</v>
@@ -14941,7 +14941,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C158" t="n">
         <v>51</v>
@@ -15581,7 +15581,7 @@
         <v>42</v>
       </c>
       <c r="C165" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>41.022527</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,7 +660,7 @@
         <v>31.8</v>
       </c>
       <c r="U2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="V2" t="n">
         <v>200</v>
@@ -753,10 +753,10 @@
         <v>47.6</v>
       </c>
       <c r="U3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="V3" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -846,10 +846,10 @@
         <v>122.7</v>
       </c>
       <c r="U4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V4" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         <v>28.3</v>
       </c>
       <c r="U5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="V5" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
         <v>141</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>1500</v>
+        <v>9150</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>141</v>
       </c>
       <c r="U7" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="V7" t="n">
         <v>300</v>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="V8" t="n">
         <v>350</v>
@@ -1311,10 +1311,10 @@
         <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>139.7</v>
       </c>
       <c r="U10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V10" t="n">
         <v>600</v>
@@ -1497,7 +1497,7 @@
         <v>59.2</v>
       </c>
       <c r="U11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="V11" t="n">
         <v>10</v>
@@ -1590,7 +1590,7 @@
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V12" t="n">
         <v>350</v>
@@ -1683,7 +1683,7 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="V13" t="n">
         <v>800</v>
@@ -1962,7 +1962,7 @@
         <v>31.8</v>
       </c>
       <c r="U16" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="V16" t="n">
         <v>200</v>
@@ -2055,7 +2055,7 @@
         <v>141</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
         <v>200</v>
@@ -2148,7 +2148,7 @@
         <v>98.2</v>
       </c>
       <c r="U18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="V18" t="n">
         <v>350</v>
@@ -2241,7 +2241,7 @@
         <v>59.2</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>200</v>
@@ -2427,7 +2427,7 @@
         <v>122.7</v>
       </c>
       <c r="U21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V21" t="n">
         <v>350</v>
@@ -2458,7 +2458,7 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>41.31798</v>
@@ -2520,10 +2520,10 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="V22" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>139.7</v>
       </c>
       <c r="U23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V23" t="n">
         <v>350</v>
@@ -2706,7 +2706,7 @@
         <v>59.2</v>
       </c>
       <c r="U24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24" t="n">
         <v>200</v>
@@ -2799,7 +2799,7 @@
         <v>139.7</v>
       </c>
       <c r="U25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V25" t="n">
         <v>350</v>
@@ -2892,7 +2892,7 @@
         <v>139.7</v>
       </c>
       <c r="U26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V26" t="n">
         <v>450</v>
@@ -2985,7 +2985,7 @@
         <v>28.3</v>
       </c>
       <c r="U27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V27" t="n">
         <v>350</v>
@@ -3078,7 +3078,7 @@
         <v>141</v>
       </c>
       <c r="U28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V28" t="n">
         <v>200</v>
@@ -3264,10 +3264,10 @@
         <v>139.7</v>
       </c>
       <c r="U30" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V30" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>122.7</v>
       </c>
       <c r="U32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V32" t="n">
         <v>500</v>
@@ -3543,7 +3543,7 @@
         <v>98.2</v>
       </c>
       <c r="U33" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V33" t="n">
         <v>350</v>
@@ -3636,10 +3636,10 @@
         <v>98.2</v>
       </c>
       <c r="U34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V34" t="n">
-        <v>10</v>
+        <v>350</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>1</v>
       </c>
       <c r="V35" t="n">
-        <v>4500</v>
+        <v>3876</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3822,10 +3822,10 @@
         <v>59.2</v>
       </c>
       <c r="U36" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="V36" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -3915,10 +3915,10 @@
         <v>47.6</v>
       </c>
       <c r="U37" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="V37" t="n">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>139.7</v>
       </c>
       <c r="U39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
         <v>1200</v>
@@ -4196,7 +4196,9 @@
       <c r="U40" t="n">
         <v>1</v>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>2000</v>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -4376,7 +4378,7 @@
         <v>31.8</v>
       </c>
       <c r="U42" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="V42" t="n">
         <v>300</v>
@@ -4469,10 +4471,10 @@
         <v>28.3</v>
       </c>
       <c r="U43" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="V43" t="n">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -4655,7 +4657,7 @@
         <v>47.6</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
         <v>200</v>
@@ -4748,10 +4750,10 @@
         <v>28.3</v>
       </c>
       <c r="U46" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V46" t="n">
-        <v>450</v>
+        <v>1200</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -4841,7 +4843,7 @@
         <v>60.2</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
@@ -4932,7 +4934,7 @@
         <v>48.5</v>
       </c>
       <c r="U48" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="V48" t="n">
         <v>300</v>
@@ -5025,10 +5027,10 @@
         <v>28.3</v>
       </c>
       <c r="U49" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V49" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5304,10 +5306,10 @@
         <v>139.7</v>
       </c>
       <c r="U52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V52" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -5488,7 +5490,7 @@
         <v>59.2</v>
       </c>
       <c r="U54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V54" t="n">
         <v>499</v>
@@ -5765,7 +5767,7 @@
         <v>139.7</v>
       </c>
       <c r="U57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V57" t="n">
         <v>6000</v>
@@ -5858,10 +5860,10 @@
         <v>122.7</v>
       </c>
       <c r="U58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V58" t="n">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -6230,7 +6232,7 @@
         <v>213.9</v>
       </c>
       <c r="U62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V62" t="n">
         <v>350</v>
@@ -6326,7 +6328,7 @@
         <v>6</v>
       </c>
       <c r="V63" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -6509,7 +6511,7 @@
         <v>184.9</v>
       </c>
       <c r="U65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V65" t="n">
         <v>18</v>
@@ -6602,7 +6604,7 @@
         <v>184.9</v>
       </c>
       <c r="U66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V66" t="n">
         <v>450</v>
@@ -6788,10 +6790,10 @@
         <v>270.6</v>
       </c>
       <c r="U68" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="V68" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
@@ -6974,10 +6976,10 @@
         <v>213.9</v>
       </c>
       <c r="U70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V70" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
@@ -7002,7 +7004,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C71" t="n">
         <v>87</v>
@@ -7067,7 +7069,7 @@
         <v>270.6</v>
       </c>
       <c r="U71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V71" t="n">
         <v>499</v>
@@ -7344,7 +7346,7 @@
         <v>270.6</v>
       </c>
       <c r="U74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V74" t="n">
         <v>1925</v>
@@ -7530,7 +7532,7 @@
         <v>270.6</v>
       </c>
       <c r="U76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr">
@@ -7556,7 +7558,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C77" t="n">
         <v>76</v>
@@ -7647,7 +7649,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C78" t="n">
         <v>76</v>
@@ -7894,7 +7896,7 @@
         <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V80" t="n">
         <v>1000</v>
@@ -8013,7 +8015,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C82" t="n">
         <v>76</v>
@@ -8199,7 +8201,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C84" t="n">
         <v>87</v>
@@ -9388,7 +9390,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C97" t="n">
         <v>76</v>
@@ -9817,11 +9819,9 @@
         <v>184.9</v>
       </c>
       <c r="U101" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" t="n">
-        <v>600</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10491,7 +10491,7 @@
         <v>25</v>
       </c>
       <c r="C109" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>41.463685</v>
@@ -11645,9 +11645,11 @@
         <v>147.5</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V121" t="n">
+        <v>1600</v>
+      </c>
       <c r="W121" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -12193,9 +12195,11 @@
         <v>147.5</v>
       </c>
       <c r="U127" t="n">
-        <v>0</v>
-      </c>
-      <c r="V127" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V127" t="n">
+        <v>1600</v>
+      </c>
       <c r="W127" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -12586,7 +12590,7 @@
         <v>58</v>
       </c>
       <c r="C132" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>40.947575</v>
@@ -13038,7 +13042,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C137" t="n">
         <v>57</v>
@@ -13558,9 +13562,11 @@
         <v>37.9</v>
       </c>
       <c r="U142" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V142" t="n">
+        <v>1800</v>
+      </c>
       <c r="W142" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13740,9 +13746,11 @@
         <v>37.9</v>
       </c>
       <c r="U144" t="n">
-        <v>0</v>
-      </c>
-      <c r="V144" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V144" t="n">
+        <v>1800</v>
+      </c>
       <c r="W144" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -13769,7 +13777,7 @@
         <v>43</v>
       </c>
       <c r="C145" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>40.869928</v>
@@ -14039,7 +14047,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C148" t="n">
         <v>56</v>
@@ -14221,7 +14229,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C150" t="n">
         <v>57</v>
@@ -14312,7 +14320,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C151" t="n">
         <v>56</v>
@@ -14496,7 +14504,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C153" t="n">
         <v>56</v>
@@ -14587,10 +14595,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C154" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>40.855744</v>
@@ -16043,7 +16051,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C170" t="n">
         <v>57</v>
@@ -17044,7 +17052,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C181" t="n">
         <v>57</v>

--- a/data/pvz_shortlist.xlsx
+++ b/data/pvz_shortlist.xlsx
@@ -660,10 +660,10 @@
         <v>47.6</v>
       </c>
       <c r="U2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V2" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>31.8</v>
       </c>
       <c r="U3" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="V3" t="n">
         <v>300</v>
@@ -846,10 +846,10 @@
         <v>141</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V4" t="n">
-        <v>9000</v>
+        <v>1600</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>32</v>
       </c>
       <c r="V5" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>141</v>
       </c>
       <c r="U6" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="V6" t="n">
         <v>300</v>
@@ -1125,7 +1125,7 @@
         <v>122.7</v>
       </c>
       <c r="U7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V7" t="n">
         <v>130</v>
@@ -1218,7 +1218,7 @@
         <v>139.7</v>
       </c>
       <c r="U8" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="V8" t="n">
         <v>350</v>
@@ -1311,7 +1311,7 @@
         <v>139.7</v>
       </c>
       <c r="U9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="V9" t="n">
         <v>100</v>
@@ -1404,7 +1404,7 @@
         <v>59.2</v>
       </c>
       <c r="U10" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="V10" t="n">
         <v>10</v>
@@ -1590,7 +1590,7 @@
         <v>141</v>
       </c>
       <c r="U12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="V12" t="n">
         <v>350</v>
@@ -1683,7 +1683,7 @@
         <v>98.2</v>
       </c>
       <c r="U13" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="V13" t="n">
         <v>800</v>
@@ -1776,7 +1776,7 @@
         <v>98.2</v>
       </c>
       <c r="U14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
         <v>350</v>
@@ -1869,10 +1869,10 @@
         <v>98.2</v>
       </c>
       <c r="U15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V15" t="n">
-        <v>950</v>
+        <v>900</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>31.8</v>
       </c>
       <c r="U16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="V16" t="n">
         <v>300</v>
@@ -2055,7 +2055,7 @@
         <v>59.2</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>200</v>
@@ -2089,19 +2089,19 @@
         <v>88</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>41.350681</v>
+        <v>41.271165</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>69.266822</v>
+        <v>69.311927</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.350681, 69.266822</t>
+          <t>41.271165, 69.311927</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Джами махалля</t>
+          <t>Ок Уй махалля</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2110,30 +2110,30 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4950</v>
+        <v>10553</v>
       </c>
       <c r="M18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="O18" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="Q18" t="n">
         <v>0.5</v>
@@ -2142,16 +2142,16 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>126</v>
+        <v>726</v>
       </c>
       <c r="T18" t="n">
-        <v>139.7</v>
+        <v>48.5</v>
       </c>
       <c r="U18" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>450</v>
+        <v>8000</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.350681,69.266822</t>
+          <t>https://www.google.com/maps?q=41.271165,69.311927</t>
         </is>
       </c>
     </row>
@@ -2182,19 +2182,19 @@
         <v>88</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>41.271165</v>
+        <v>41.350681</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>69.311927</v>
+        <v>69.266822</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.271165, 69.311927</t>
+          <t>41.350681, 69.266822</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ок Уй махалля</t>
+          <t>Джами махалля</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2203,30 +2203,30 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Юнусабадский район</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>10553</v>
+        <v>4950</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="P19" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="Q19" t="n">
         <v>0.5</v>
@@ -2235,16 +2235,16 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>726</v>
+        <v>126</v>
       </c>
       <c r="T19" t="n">
-        <v>48.5</v>
+        <v>139.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="V19" t="n">
-        <v>8000</v>
+        <v>450</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271165,69.311927</t>
+          <t>https://www.google.com/maps?q=41.350681,69.266822</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         <v>139.7</v>
       </c>
       <c r="U21" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V21" t="n">
         <v>600</v>
@@ -2520,7 +2520,7 @@
         <v>139.7</v>
       </c>
       <c r="U22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V22" t="n">
         <v>350</v>
@@ -2613,10 +2613,10 @@
         <v>122.7</v>
       </c>
       <c r="U23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>141</v>
       </c>
       <c r="U25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V25" t="n">
         <v>200</v>
@@ -3078,10 +3078,10 @@
         <v>28.3</v>
       </c>
       <c r="U28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>41.315906</v>
@@ -3171,7 +3171,7 @@
         <v>98.2</v>
       </c>
       <c r="U29" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="V29" t="n">
         <v>1000</v>
@@ -3264,10 +3264,10 @@
         <v>141</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>2600</v>
+        <v>1100</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3357,10 +3357,10 @@
         <v>139.7</v>
       </c>
       <c r="U31" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="V31" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3543,10 +3543,10 @@
         <v>139.7</v>
       </c>
       <c r="U33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V33" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -3638,9 +3638,7 @@
       <c r="U34" t="n">
         <v>1</v>
       </c>
-      <c r="V34" t="n">
-        <v>300</v>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -3729,10 +3727,10 @@
         <v>122.7</v>
       </c>
       <c r="U35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V35" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -3822,7 +3820,7 @@
         <v>98.2</v>
       </c>
       <c r="U36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V36" t="n">
         <v>10</v>
@@ -4008,7 +4006,7 @@
         <v>98.2</v>
       </c>
       <c r="U38" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="V38" t="n">
         <v>350</v>
@@ -4194,10 +4192,10 @@
         <v>59.2</v>
       </c>
       <c r="U40" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V40" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4287,10 +4285,10 @@
         <v>47.6</v>
       </c>
       <c r="U41" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="V41" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4507,14 +4505,14 @@
         <v>77</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>41.401782</v>
+        <v>41.405202</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>69.458556</v>
+        <v>69.458668</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>41.401782, 69.458556</t>
+          <t>41.405202, 69.458668</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4528,7 +4526,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4539,7 +4537,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3473</v>
+        <v>3603</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -4581,7 +4579,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.401782,69.458556</t>
+          <t>https://www.google.com/maps?q=41.405202,69.458668</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4655,7 @@
         <v>59.2</v>
       </c>
       <c r="U45" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V45" t="n">
         <v>200</v>
@@ -4688,7 +4686,7 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>41.390081</v>
@@ -4843,7 +4841,7 @@
         <v>31.8</v>
       </c>
       <c r="U47" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="V47" t="n">
         <v>300</v>
@@ -4936,10 +4934,10 @@
         <v>28.3</v>
       </c>
       <c r="U48" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V48" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -4967,22 +4965,22 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>41.363189</v>
+        <v>41.283644</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>69.330555</v>
+        <v>69.28462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>41.363189, 69.330555</t>
+          <t>41.283644, 69.284620</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Актепа махалля</t>
+          <t>Сарыкулька</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4991,30 +4989,30 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Юнусабадский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2006</v>
+        <v>5986</v>
       </c>
       <c r="M49" t="n">
         <v>5</v>
       </c>
       <c r="N49" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="O49" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="P49" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="Q49" t="n">
         <v>0.5</v>
@@ -5026,13 +5024,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>139.7</v>
+        <v>48.5</v>
       </c>
       <c r="U49" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="V49" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5046,7 +5044,7 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.363189,69.330555</t>
+          <t>https://www.google.com/maps?q=41.283644,69.284620</t>
         </is>
       </c>
     </row>
@@ -5063,19 +5061,19 @@
         <v>73</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>41.283644</v>
+        <v>41.271397</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>69.28462</v>
+        <v>69.20517700000001</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>41.283644, 69.284620</t>
+          <t>41.271397, 69.205177</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Сарыкулька</t>
+          <t>Наккашлык</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5084,30 +5082,30 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>5986</v>
+        <v>10663</v>
       </c>
       <c r="M50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N50" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="O50" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P50" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="Q50" t="n">
         <v>0.5</v>
@@ -5119,13 +5117,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>48.5</v>
+        <v>28.3</v>
       </c>
       <c r="U50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="V50" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5139,7 +5137,7 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.283644,69.284620</t>
+          <t>https://www.google.com/maps?q=41.271397,69.205177</t>
         </is>
       </c>
     </row>
@@ -5156,19 +5154,19 @@
         <v>73</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>41.271397</v>
+        <v>41.254507</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>69.20517700000001</v>
+        <v>69.37862699999999</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>41.271397, 69.205177</t>
+          <t>41.254507, 69.378627</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Наккашлык</t>
+          <t>Сувсоз-2 (Водник)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5177,30 +5175,30 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>10663</v>
+        <v>10644</v>
       </c>
       <c r="M51" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N51" t="n">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="O51" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="P51" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
         <v>0.5</v>
@@ -5212,14 +5210,12 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>28.3</v>
+        <v>60.2</v>
       </c>
       <c r="U51" t="n">
-        <v>14</v>
-      </c>
-      <c r="V51" t="n">
-        <v>450</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5232,7 +5228,7 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.271397,69.205177</t>
+          <t>https://www.google.com/maps?q=41.254507,69.378627</t>
         </is>
       </c>
     </row>
@@ -5246,22 +5242,22 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>41.254507</v>
+        <v>41.283152</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>69.37862699999999</v>
+        <v>69.217376</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>41.254507, 69.378627</t>
+          <t>41.283152, 69.217376</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Сувсоз-2 (Водник)</t>
+          <t>Чиланзар-4</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5270,30 +5266,30 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Чиланзарский район</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>10644</v>
+        <v>8748</v>
       </c>
       <c r="M52" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N52" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O52" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="Q52" t="n">
         <v>0.5</v>
@@ -5305,12 +5301,14 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>60.2</v>
+        <v>28.3</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="V52" t="n">
+        <v>500</v>
+      </c>
       <c r="W52" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -5323,7 +5321,7 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.254507,69.378627</t>
+          <t>https://www.google.com/maps?q=41.283152,69.217376</t>
         </is>
       </c>
     </row>
@@ -5340,19 +5338,19 @@
         <v>72</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>41.283152</v>
+        <v>41.252288</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>69.217376</v>
+        <v>69.315309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>41.283152, 69.217376</t>
+          <t>41.252288, 69.315309</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Чиланзар-4</t>
+          <t>Билимдан махалля</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5368,23 +5366,23 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Чиланзарский район</t>
+          <t>Мирабадский район</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>8748</v>
+        <v>9192</v>
       </c>
       <c r="M53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N53" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="O53" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="Q53" t="n">
         <v>0.5</v>
@@ -5396,13 +5394,13 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>28.3</v>
+        <v>48.5</v>
       </c>
       <c r="U53" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="V53" t="n">
-        <v>450</v>
+        <v>1200</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -5416,7 +5414,7 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.283152,69.217376</t>
+          <t>https://www.google.com/maps?q=41.252288,69.315309</t>
         </is>
       </c>
     </row>
@@ -5433,51 +5431,51 @@
         <v>72</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>41.252288</v>
+        <v>41.228062</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>69.315309</v>
+        <v>69.330381</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>41.252288, 69.315309</t>
+          <t>41.228062, 69.330381</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Билимдан махалля</t>
+          <t>Бектемир</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>район города</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Мирабадский район</t>
+          <t>Бектемирский район</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>9192</v>
+        <v>4317</v>
       </c>
       <c r="M54" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N54" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P54" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="Q54" t="n">
         <v>0.5</v>
@@ -5489,7 +5487,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>48.5</v>
+        <v>60.2</v>
       </c>
       <c r="U54" t="n">
         <v>3</v>
@@ -5509,7 +5507,7 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.252288,69.315309</t>
+          <t>https://www.google.com/maps?q=41.228062,69.330381</t>
         </is>
       </c>
     </row>
@@ -5526,51 +5524,51 @@
         <v>72</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>41.228062</v>
+        <v>41.277832</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>69.330381</v>
+        <v>69.130234</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>41.228062, 69.330381</t>
+          <t>41.277832, 69.130234</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Бектемир</t>
+          <t>Дамачи</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>район города</t>
+          <t>посёлок</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Бектемирский район</t>
+          <t>Зангиатинский район</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>4317</v>
+        <v>1699</v>
       </c>
       <c r="M55" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N55" t="n">
         <v>7</v>
       </c>
       <c r="O55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P55" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="Q55" t="n">
         <v>0.5</v>
@@ -5582,13 +5580,13 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>60.2</v>
+        <v>184.9</v>
       </c>
       <c r="U55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V55" t="n">
-        <v>1200</v>
+        <v>2</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -5602,7 +5600,7 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.228062,69.330381</t>
+          <t>https://www.google.com/maps?q=41.277832,69.130234</t>
         </is>
       </c>
     </row>
@@ -5616,54 +5614,54 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>41.277832</v>
+        <v>41.270832</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>69.130234</v>
+        <v>69.23679199999999</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>41.277832, 69.130234</t>
+          <t>41.270832, 69.236792</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Дамачи</t>
+          <t>Дилбулак махалля</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>посёлок</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Зангиатинский район</t>
+          <t>Яккасарайский район</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1699</v>
+        <v>11138</v>
       </c>
       <c r="M56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="P56" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="Q56" t="n">
         <v>0.5</v>
@@ -5675,13 +5673,13 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>184.9</v>
+        <v>31.8</v>
       </c>
       <c r="U56" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="V56" t="n">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -5695,7 +5693,7 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.277832,69.130234</t>
+          <t>https://www.google.com/maps?q=41.270832,69.236792</t>
         </is>
       </c>
     </row>
@@ -5709,22 +5707,22 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>41.270832</v>
+        <v>41.378753</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>69.23679199999999</v>
+        <v>69.228041</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>41.270832, 69.236792</t>
+          <t>41.378753, 69.228041</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Дилбулак махалля</t>
+          <t>Ахил махалля</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5733,30 +5731,30 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Яккасарайский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>11138</v>
+        <v>3771</v>
       </c>
       <c r="M57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="O57" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="P57" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="Q57" t="n">
         <v>0.5</v>
@@ -5768,13 +5766,13 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>31.8</v>
+        <v>59.2</v>
       </c>
       <c r="U57" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="V57" t="n">
-        <v>300</v>
+        <v>499</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -5788,7 +5786,7 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.270832,69.236792</t>
+          <t>https://www.google.com/maps?q=41.378753,69.228041</t>
         </is>
       </c>
     </row>
@@ -5805,19 +5803,19 @@
         <v>70</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>41.378753</v>
+        <v>41.379175</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>69.228041</v>
+        <v>69.20428699999999</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>41.378753, 69.228041</t>
+          <t>41.379175, 69.204287</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ахил махалля</t>
+          <t>Нихол махалля</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5837,19 +5835,19 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3771</v>
+        <v>3783</v>
       </c>
       <c r="M58" t="n">
         <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q58" t="n">
         <v>0.5</v>
@@ -5864,7 +5862,7 @@
         <v>59.2</v>
       </c>
       <c r="U58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V58" t="n">
         <v>499</v>
@@ -5881,7 +5879,7 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.378753,69.228041</t>
+          <t>https://www.google.com/maps?q=41.379175,69.204287</t>
         </is>
       </c>
     </row>
@@ -5895,22 +5893,22 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>41.379175</v>
+        <v>41.195341</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>69.20428699999999</v>
+        <v>69.25040199999999</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>41.379175, 69.204287</t>
+          <t>41.195341, 69.250402</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Нихол махалля</t>
+          <t>Дарьябуйи махалля</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5919,27 +5917,27 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Алмазарский район</t>
+          <t>Янгихаётский район</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3783</v>
+        <v>1884</v>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P59" t="n">
         <v>7</v>
@@ -5954,13 +5952,13 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>59.2</v>
+        <v>122.7</v>
       </c>
       <c r="U59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V59" t="n">
-        <v>499</v>
+        <v>130</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -5974,7 +5972,7 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.379175,69.204287</t>
+          <t>https://www.google.com/maps?q=41.195341,69.250402</t>
         </is>
       </c>
     </row>
@@ -5988,27 +5986,27 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>41.195341</v>
+        <v>41.174834</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>69.25040199999999</v>
+        <v>69.249804</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>41.195341, 69.250402</t>
+          <t>41.174834, 69.249804</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Дарьябуйи махалля</t>
+          <t>Бинокор</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>махалля</t>
+          <t>село</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -6023,19 +6021,19 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1884</v>
+        <v>2032</v>
       </c>
       <c r="M60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0.5</v>
@@ -6050,10 +6048,10 @@
         <v>122.7</v>
       </c>
       <c r="U60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V60" t="n">
-        <v>130</v>
+        <v>21000</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -6062,12 +6060,12 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>3 из 3</t>
+          <t>2 из 3</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.195341,69.250402</t>
+          <t>https://www.google.com/maps?q=41.174834,69.249804</t>
         </is>
       </c>
     </row>
@@ -6081,27 +6079,27 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>41.174834</v>
+        <v>41.366571</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>69.249804</v>
+        <v>69.23957</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>41.174834, 69.249804</t>
+          <t>41.366571, 69.239570</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Бинокор</t>
+          <t>Каракамыш 1/4</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>село</t>
+          <t>махалля</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -6112,23 +6110,23 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Янгихаётский район</t>
+          <t>Алмазарский район</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2032</v>
+        <v>1803</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q61" t="n">
         <v>0.5</v>
@@ -6140,13 +6138,13 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>122.7</v>
+        <v>59.2</v>
       </c>
       <c r="U61" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V61" t="n">
-        <v>21000</v>
+        <v>10</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -6155,12 +6153,12 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2 из 3</t>
+          <t>3 из 3</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=41.174834,69.249804</t>
+          <t>https://www.google.com/maps?q=41.366571,69.239570</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6263,7 @@
         <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>41.337191</v>
@@ -6420,10 +6418,10 @@
         <v>184.9</v>
       </c>
       <c r="U64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V64" t="n">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -6513,7 +6511,7 @@
         <v>213.9</v>
       </c>
       <c r="U65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V65" t="n">
         <v>100</v>
@@ -6606,10 +6604,10 @@
         <v>270.6</v>
       </c>
       <c r="U66" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V66" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
@@ -6914,7 +6912,7 @@
         <v>5</v>
       </c>
       <c r="C70" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>41.387795</v>
@@ -6976,7 +6974,7 @@
         <v>270.6</v>
       </c>
       <c r="U70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V70" t="n">
         <v>499</v>
@@ -7004,7 +7002,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C71" t="n">
         <v>81</v>
@@ -7095,7 +7093,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C72" t="n">
         <v>87</v>
@@ -7160,7 +7158,7 @@
         <v>184.9</v>
       </c>
       <c r="U72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V72" t="n">
         <v>3900</v>
@@ -7437,10 +7435,10 @@
         <v>270.6</v>
       </c>
       <c r="U75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V75" t="n">
-        <v>1925</v>
+        <v>6000</v>
       </c>
       <c r="W75" t="inlineStr">
         <is>
@@ -7465,7 +7463,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C76" t="n">
         <v>78</v>
@@ -7556,7 +7554,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C77" t="n">
         <v>78</v>
@@ -7647,7 +7645,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C78" t="n">
         <v>80</v>
@@ -7894,7 +7892,7 @@
         <v>213.9</v>
       </c>
       <c r="U80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V80" t="n">
         <v>1000</v>
@@ -7925,7 +7923,7 @@
         <v>56</v>
       </c>
       <c r="C81" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>41.401398</v>
@@ -8080,7 +8078,7 @@
         <v>213.9</v>
       </c>
       <c r="U82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V82" t="n">
         <v>1100</v>
@@ -8108,7 +8106,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C83" t="n">
         <v>87</v>
@@ -8176,7 +8174,7 @@
         <v>1</v>
       </c>
       <c r="V83" t="n">
-        <v>1925</v>
+        <v>1200</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8359,7 +8357,7 @@
         <v>213.9</v>
       </c>
       <c r="U85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V85" t="n">
         <v>1100</v>
@@ -8387,7 +8385,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C86" t="n">
         <v>80</v>
@@ -8660,7 +8658,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C89" t="n">
         <v>78</v>
@@ -8907,7 +8905,7 @@
         <v>184.9</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr">
@@ -9297,7 +9295,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C96" t="n">
         <v>81</v>
@@ -9388,7 +9386,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C97" t="n">
         <v>81</v>
@@ -9453,9 +9451,11 @@
         <v>270.6</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
-      </c>
-      <c r="V97" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V97" t="n">
+        <v>1200</v>
+      </c>
       <c r="W97" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -9755,7 +9755,7 @@
         <v>39</v>
       </c>
       <c r="C101" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>41.445517</v>
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C105" t="n">
         <v>81</v>
@@ -10276,9 +10276,11 @@
         <v>40.8</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V106" t="n">
+        <v>7000</v>
+      </c>
       <c r="W106" t="inlineStr">
         <is>
           <t>рекомендуемая</t>
@@ -10458,10 +10460,10 @@
         <v>40.8</v>
       </c>
       <c r="U108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V108" t="n">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="W108" t="inlineStr">
         <is>
@@ -10668,7 +10670,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C111" t="n">
         <v>78</v>
@@ -15049,7 +15051,7 @@
         <v>41</v>
       </c>
       <c r="C159" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>41.622198</v>
@@ -16414,7 +16416,7 @@
         <v>30</v>
       </c>
       <c r="C174" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D174" s="2" t="n">
         <v>40.97953</v>
